--- a/public/exports-from-60-with-coowners/29189919.xlsx
+++ b/public/exports-from-60-with-coowners/29189919.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">

--- a/public/exports-from-60-with-coowners/29189919.xlsx
+++ b/public/exports-from-60-with-coowners/29189919.xlsx
@@ -10926,20 +10926,20 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">4455442</t>
+          <t xml:space="preserve">4455442, 100194390</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J146">
-        <v>2812</v>
+        <v>1173</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311465122</t>
+          <t xml:space="preserve">311465121</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -10991,30 +10991,30 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevejen 6</t>
+          <t xml:space="preserve">Skolegade 31</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">6933</t>
+          <t xml:space="preserve">7280</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">4455442</t>
+          <t xml:space="preserve">9455769</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J147">
-        <v>386</v>
+        <v>1152</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311465119</t>
+          <t xml:space="preserve">311465344</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-04</t>
+          <t xml:space="preserve">2030-10-05</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11066,30 +11066,30 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevejen 6</t>
+          <t xml:space="preserve">Klejnstrupvej 2</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">6933</t>
+          <t xml:space="preserve">7550</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">4455442, 100194390</t>
+          <t xml:space="preserve">4506137</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J148">
-        <v>1173</v>
+        <v>108</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311465121</t>
+          <t xml:space="preserve">311471526</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-04</t>
+          <t xml:space="preserve">2030-10-30</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11141,30 +11141,30 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 31</t>
+          <t xml:space="preserve">Kollundvej 15</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">7280</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">9455769</t>
+          <t xml:space="preserve">4453257</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J149">
-        <v>1152</v>
+        <v>282</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311465344</t>
+          <t xml:space="preserve">311471519</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11174,7 +11174,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-05</t>
+          <t xml:space="preserve">2030-10-30</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -11216,30 +11216,30 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klejnstrupvej 2</t>
+          <t xml:space="preserve">Skolegade 13B</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">7550</t>
+          <t xml:space="preserve">7280</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">4506137</t>
+          <t xml:space="preserve">9455769</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J150">
-        <v>108</v>
+        <v>725</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311471526</t>
+          <t xml:space="preserve">311471524</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11291,30 +11291,30 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kollundvej 15</t>
+          <t xml:space="preserve">Soldalen 4</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7480</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">4453257</t>
+          <t xml:space="preserve">4462904</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J151">
-        <v>282</v>
+        <v>380</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311471519</t>
+          <t xml:space="preserve">311471529</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 13B</t>
+          <t xml:space="preserve">Torvegade 2</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -11376,20 +11376,20 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">9455769</t>
+          <t xml:space="preserve">9063551</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J152">
-        <v>725</v>
+        <v>93</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311471524</t>
+          <t xml:space="preserve">311471520</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11441,17 +11441,17 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Soldalen 4</t>
+          <t xml:space="preserve">Brændgårdvej 20</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">7480</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">4462904</t>
+          <t xml:space="preserve">5706289</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -11460,11 +11460,11 @@
         </is>
       </c>
       <c r="J153">
-        <v>380</v>
+        <v>7818</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311471529</t>
+          <t xml:space="preserve">311475497</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -11474,7 +11474,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-30</t>
+          <t xml:space="preserve">2030-11-13</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11516,17 +11516,17 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvegade 2</t>
+          <t xml:space="preserve">Bethaniagade 10</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">7280</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">9063551</t>
+          <t xml:space="preserve">8591744</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -11535,21 +11535,21 @@
         </is>
       </c>
       <c r="J154">
-        <v>93</v>
+        <v>3391</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311471520</t>
+          <t xml:space="preserve">311868826</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-30</t>
+          <t xml:space="preserve">2030-12-07</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11591,7 +11591,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændgårdvej 20</t>
+          <t xml:space="preserve">Godsbanevej 2</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -11601,20 +11601,20 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5706289</t>
+          <t xml:space="preserve">5696196</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J155">
-        <v>7818</v>
+        <v>247</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475497</t>
+          <t xml:space="preserve">311480997</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-13</t>
+          <t xml:space="preserve">2030-12-07</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11666,17 +11666,17 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyvelvej 5</t>
+          <t xml:space="preserve">Torvet 5</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">7550</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">4506406</t>
+          <t xml:space="preserve">5697356</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -11685,11 +11685,11 @@
         </is>
       </c>
       <c r="J156">
-        <v>498</v>
+        <v>2786</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475754</t>
+          <t xml:space="preserve">311480990</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-15</t>
+          <t xml:space="preserve">2030-12-07</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11741,30 +11741,30 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyvelvej 5</t>
+          <t xml:space="preserve">Bethaniagade 1</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">7550</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">4506406</t>
+          <t xml:space="preserve">5697356</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J157">
-        <v>77</v>
+        <v>3979</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311475755</t>
+          <t xml:space="preserve">311481616</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-15</t>
+          <t xml:space="preserve">2030-12-09</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bethaniagade 10</t>
+          <t xml:space="preserve">Brorsonsvej 6</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -11826,30 +11826,30 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">8591744</t>
+          <t xml:space="preserve">5706491</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J158">
-        <v>3391</v>
+        <v>1380</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868826</t>
+          <t xml:space="preserve">311481632</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-07</t>
+          <t xml:space="preserve">2030-12-09</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Godsbanevej 2</t>
+          <t xml:space="preserve">H.P. Hansens Vej 6B</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -11901,20 +11901,20 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">5696196</t>
+          <t xml:space="preserve">5704686</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J159">
-        <v>247</v>
+        <v>285</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311480997</t>
+          <t xml:space="preserve">311482350</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11924,7 +11924,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-07</t>
+          <t xml:space="preserve">2030-12-11</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvet 5</t>
+          <t xml:space="preserve">Kollundvej 35</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">5697356</t>
+          <t xml:space="preserve">8966326</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -11985,11 +11985,11 @@
         </is>
       </c>
       <c r="J160">
-        <v>2786</v>
+        <v>232</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311480990</t>
+          <t xml:space="preserve">311482158</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -11999,7 +11999,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-07</t>
+          <t xml:space="preserve">2030-12-11</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bethaniagade 1</t>
+          <t xml:space="preserve">Gilmosevej 22</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -12051,20 +12051,20 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">5697356</t>
+          <t xml:space="preserve">100048226</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J161">
-        <v>3979</v>
+        <v>186</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311481616</t>
+          <t xml:space="preserve">311482454</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-09</t>
+          <t xml:space="preserve">2030-12-13</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -12116,7 +12116,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brorsonsvej 6</t>
+          <t xml:space="preserve">H.P. Hansens Vej 6</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -12126,20 +12126,20 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">5706491</t>
+          <t xml:space="preserve">5704686</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J162">
-        <v>1380</v>
+        <v>247</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311481632</t>
+          <t xml:space="preserve">311482452</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-09</t>
+          <t xml:space="preserve">2030-12-13</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -12191,7 +12191,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">H.P. Hansens Vej 6B</t>
+          <t xml:space="preserve">H.P. Hansens Vej 6</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -12206,15 +12206,15 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J163">
-        <v>285</v>
+        <v>138</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311482350</t>
+          <t xml:space="preserve">311482453</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -12224,7 +12224,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-11</t>
+          <t xml:space="preserve">2030-12-13</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kollundvej 35</t>
+          <t xml:space="preserve">Asylgade 1</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -12276,7 +12276,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">8966326</t>
+          <t xml:space="preserve">4457628</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -12285,11 +12285,11 @@
         </is>
       </c>
       <c r="J164">
-        <v>232</v>
+        <v>278</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311482158</t>
+          <t xml:space="preserve">311482554</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-11</t>
+          <t xml:space="preserve">2030-12-14</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gilmosevej 22</t>
+          <t xml:space="preserve">Hammershusvej 7</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -12351,20 +12351,20 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">100048226</t>
+          <t xml:space="preserve">5704845</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J165">
-        <v>186</v>
+        <v>103</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311482454</t>
+          <t xml:space="preserve">311482557</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-13</t>
+          <t xml:space="preserve">2030-12-14</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">H.P. Hansens Vej 6</t>
+          <t xml:space="preserve">Hammershusvej 7</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -12426,7 +12426,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">5704686</t>
+          <t xml:space="preserve">5704845</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -12435,11 +12435,11 @@
         </is>
       </c>
       <c r="J166">
-        <v>247</v>
+        <v>1208</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311482452</t>
+          <t xml:space="preserve">311483577</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-13</t>
+          <t xml:space="preserve">2030-12-17</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">H.P. Hansens Vej 6</t>
+          <t xml:space="preserve">Hammershusvej 7</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">5704686</t>
+          <t xml:space="preserve">5704845</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -12510,11 +12510,11 @@
         </is>
       </c>
       <c r="J167">
-        <v>138</v>
+        <v>634</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311482453</t>
+          <t xml:space="preserve">311483578</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-13</t>
+          <t xml:space="preserve">2030-12-17</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12566,17 +12566,17 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asylgade 1</t>
+          <t xml:space="preserve">Gyvelvej 4</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7490</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">4457628</t>
+          <t xml:space="preserve">4433703</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -12585,11 +12585,11 @@
         </is>
       </c>
       <c r="J168">
-        <v>278</v>
+        <v>92</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311482554</t>
+          <t xml:space="preserve">311486253</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-14</t>
+          <t xml:space="preserve">2031-01-07</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hammershusvej 7</t>
+          <t xml:space="preserve">Engbjerg 21</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -12651,20 +12651,20 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">5704845</t>
+          <t xml:space="preserve">4456901</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J169">
-        <v>103</v>
+        <v>2078</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311482557</t>
+          <t xml:space="preserve">311488098</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -12674,7 +12674,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-14</t>
+          <t xml:space="preserve">2031-01-15</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12716,7 +12716,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hammershusvej 7</t>
+          <t xml:space="preserve">Engbjerg 21</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -12726,20 +12726,20 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">5704845</t>
+          <t xml:space="preserve">4456901</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J170">
-        <v>1208</v>
+        <v>1199</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483577</t>
+          <t xml:space="preserve">311488100</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-17</t>
+          <t xml:space="preserve">2031-01-15</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12791,7 +12791,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hammershusvej 7</t>
+          <t xml:space="preserve">Engbjerg 21</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -12801,20 +12801,20 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">5704845</t>
+          <t xml:space="preserve">4456901</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J171">
-        <v>634</v>
+        <v>587</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311483578</t>
+          <t xml:space="preserve">311488102</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-12-17</t>
+          <t xml:space="preserve">2031-01-15</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12866,30 +12866,30 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyvelvej 4</t>
+          <t xml:space="preserve">Engbjerg 23</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">7490</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">4433703</t>
+          <t xml:space="preserve">4456901</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J172">
-        <v>92</v>
+        <v>1174</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311486253</t>
+          <t xml:space="preserve">311488103</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -12899,7 +12899,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-07</t>
+          <t xml:space="preserve">2031-01-15</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12941,17 +12941,17 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engbjerg 21</t>
+          <t xml:space="preserve">Jernbanegade 2</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7490</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">4456901</t>
+          <t xml:space="preserve">4435005</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -12960,11 +12960,11 @@
         </is>
       </c>
       <c r="J173">
-        <v>2078</v>
+        <v>309</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311488098</t>
+          <t xml:space="preserve">311488032</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engbjerg 21</t>
+          <t xml:space="preserve">Vesterlindvej 21</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -13026,25 +13026,25 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">4456901</t>
+          <t xml:space="preserve">4452247</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J174">
-        <v>1199</v>
+        <v>482</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t xml:space="preserve">311488100</t>
+          <t xml:space="preserve">311488095</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engbjerg 21</t>
+          <t xml:space="preserve">Gl. Skolevej 35</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -13101,20 +13101,20 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">4456901</t>
+          <t xml:space="preserve">5699393</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J175">
-        <v>587</v>
+        <v>3690</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311488102</t>
+          <t xml:space="preserve">311500097</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-15</t>
+          <t xml:space="preserve">2031-03-03</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engbjerg 23</t>
+          <t xml:space="preserve">Gl. Skolevej 35</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">4456901</t>
+          <t xml:space="preserve">5699393</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -13185,11 +13185,11 @@
         </is>
       </c>
       <c r="J176">
-        <v>1174</v>
+        <v>3682</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311488103</t>
+          <t xml:space="preserve">311500098</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-15</t>
+          <t xml:space="preserve">2031-03-03</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -13241,30 +13241,30 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 2</t>
+          <t xml:space="preserve">Gl. Skolevej 35</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">7490</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">4435005</t>
+          <t xml:space="preserve">5699393</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J177">
-        <v>309</v>
+        <v>1529</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311488032</t>
+          <t xml:space="preserve">311500100</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -13274,7 +13274,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-15</t>
+          <t xml:space="preserve">2031-03-03</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -13316,40 +13316,40 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterlindvej 21</t>
+          <t xml:space="preserve">Soldalen 8</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7480</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">4452247</t>
+          <t xml:space="preserve">8453536</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J178">
-        <v>482</v>
+        <v>2260</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311488095</t>
+          <t xml:space="preserve">311500079</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-01-15</t>
+          <t xml:space="preserve">2031-03-03</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13406,15 +13406,15 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J179">
-        <v>3690</v>
+        <v>1438</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311500097</t>
+          <t xml:space="preserve">311502543</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-03</t>
+          <t xml:space="preserve">2031-03-11</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13466,30 +13466,30 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Skolevej 35</t>
+          <t xml:space="preserve">Skalmejevej 33</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7451</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699393</t>
+          <t xml:space="preserve">1805456</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J180">
-        <v>3682</v>
+        <v>4065</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311500098</t>
+          <t xml:space="preserve">311502547</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -13499,7 +13499,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-03</t>
+          <t xml:space="preserve">2031-03-11</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13541,30 +13541,30 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Skolevej 35</t>
+          <t xml:space="preserve">Skalmejevej 33</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7451</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699393</t>
+          <t xml:space="preserve">1805456</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J181">
-        <v>1529</v>
+        <v>582</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311500100</t>
+          <t xml:space="preserve">311502548</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -13574,7 +13574,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-03</t>
+          <t xml:space="preserve">2031-03-11</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13616,30 +13616,30 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Soldalen 8</t>
+          <t xml:space="preserve">Tjelevej 25</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">7480</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">8453536</t>
+          <t xml:space="preserve">5707346</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J182">
-        <v>2260</v>
+        <v>1821</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311500079</t>
+          <t xml:space="preserve">311507310</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -13649,7 +13649,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-03</t>
+          <t xml:space="preserve">2031-03-26</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Skolevej 35</t>
+          <t xml:space="preserve">Tjelevej 25</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -13701,20 +13701,20 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699393</t>
+          <t xml:space="preserve">5707346</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J183">
-        <v>1438</v>
+        <v>914</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311502543</t>
+          <t xml:space="preserve">311507300</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -13724,7 +13724,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-11</t>
+          <t xml:space="preserve">2031-03-26</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13766,30 +13766,30 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skalmejevej 33</t>
+          <t xml:space="preserve">Tjelevej 25</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">7451</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805456</t>
+          <t xml:space="preserve">5707346</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J184">
-        <v>4065</v>
+        <v>1214</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311502547</t>
+          <t xml:space="preserve">311507302</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -13799,7 +13799,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-11</t>
+          <t xml:space="preserve">2031-03-26</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13841,30 +13841,30 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skalmejevej 33</t>
+          <t xml:space="preserve">Tjelevej 25</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">7451</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805456</t>
+          <t xml:space="preserve">5707346</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J185">
-        <v>582</v>
+        <v>1296</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311502548</t>
+          <t xml:space="preserve">311507304</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-11</t>
+          <t xml:space="preserve">2031-03-26</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13931,15 +13931,15 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J186">
-        <v>1821</v>
+        <v>1390</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507310</t>
+          <t xml:space="preserve">311507307</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -14006,15 +14006,15 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J187">
-        <v>914</v>
+        <v>4684</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507300</t>
+          <t xml:space="preserve">311507298</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -14066,17 +14066,17 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjelevej 25</t>
+          <t xml:space="preserve">Velhustedvej 10</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">6933</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">5707346</t>
+          <t xml:space="preserve">1805364</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -14085,21 +14085,21 @@
         </is>
       </c>
       <c r="J188">
-        <v>1214</v>
+        <v>1515</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507302</t>
+          <t xml:space="preserve">311873970</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-26</t>
+          <t xml:space="preserve">2031-04-09</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -14141,17 +14141,17 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjelevej 25</t>
+          <t xml:space="preserve">Velhustedvej 10</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">6933</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">5707346</t>
+          <t xml:space="preserve">1805364</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -14160,11 +14160,11 @@
         </is>
       </c>
       <c r="J189">
-        <v>1296</v>
+        <v>701</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507304</t>
+          <t xml:space="preserve">311511168</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -14174,7 +14174,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-26</t>
+          <t xml:space="preserve">2031-04-09</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -14216,30 +14216,30 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjelevej 25</t>
+          <t xml:space="preserve">Velhustedvej 6</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">6933</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">5707346</t>
+          <t xml:space="preserve">1805364</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J190">
-        <v>1390</v>
+        <v>413</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507307</t>
+          <t xml:space="preserve">311511163</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -14249,7 +14249,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-26</t>
+          <t xml:space="preserve">2031-04-09</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -14291,30 +14291,30 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjelevej 25</t>
+          <t xml:space="preserve">Velhustedvej 10</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">6933</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">5707346</t>
+          <t xml:space="preserve">1805364</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J191">
-        <v>4684</v>
+        <v>1096</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311507298</t>
+          <t xml:space="preserve">311511782</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -14324,7 +14324,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-26</t>
+          <t xml:space="preserve">2031-04-13</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -14381,25 +14381,25 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J192">
-        <v>1515</v>
+        <v>423</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311873970</t>
+          <t xml:space="preserve">311511784</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-09</t>
+          <t xml:space="preserve">2031-04-13</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -14441,7 +14441,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Velhustedvej 10</t>
+          <t xml:space="preserve">Velhustedvej 12A</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -14456,15 +14456,15 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J193">
-        <v>701</v>
+        <v>1052</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311511168</t>
+          <t xml:space="preserve">311513130</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -14474,7 +14474,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-09</t>
+          <t xml:space="preserve">2031-04-16</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14501,12 +14501,12 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herning Kommune</t>
+          <t xml:space="preserve">MCH A/S</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -14516,17 +14516,17 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Velhustedvej 6</t>
+          <t xml:space="preserve">Kaj Zartows Vej 5</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">6933</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805364</t>
+          <t xml:space="preserve">100291056, 100291057, 100291058</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -14535,21 +14535,21 @@
         </is>
       </c>
       <c r="J194">
-        <v>413</v>
+        <v>11483</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311511163</t>
+          <t xml:space="preserve">311532840</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+          <t xml:space="preserve">Scanenergi A/S</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-09</t>
+          <t xml:space="preserve">2031-07-01</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Velhustedvej 10</t>
+          <t xml:space="preserve">Jernbanegade 1</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -14601,20 +14601,20 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805364</t>
+          <t xml:space="preserve">4433294</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J195">
-        <v>1096</v>
+        <v>324</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311511782</t>
+          <t xml:space="preserve">311535258</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -14624,7 +14624,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-13</t>
+          <t xml:space="preserve">2031-07-12</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14666,7 +14666,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Velhustedvej 10</t>
+          <t xml:space="preserve">Kirkepladsen 1B</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -14676,20 +14676,20 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805364</t>
+          <t xml:space="preserve">4455488</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J196">
-        <v>423</v>
+        <v>190</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311511784</t>
+          <t xml:space="preserve">311535252</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-13</t>
+          <t xml:space="preserve">2031-07-12</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14741,30 +14741,30 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Velhustedvej 12A</t>
+          <t xml:space="preserve">Burgårdsvej 8</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t xml:space="preserve">6933</t>
+          <t xml:space="preserve">7480</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805364</t>
+          <t xml:space="preserve">4462912</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J197">
-        <v>1052</v>
+        <v>848</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311513130</t>
+          <t xml:space="preserve">311539387</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -14774,7 +14774,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-04-16</t>
+          <t xml:space="preserve">2031-08-06</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14801,12 +14801,12 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t xml:space="preserve">MCH A/S</t>
+          <t xml:space="preserve">Herning Kommune</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -14816,17 +14816,17 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaj Zartows Vej 5</t>
+          <t xml:space="preserve">Røddingvej 21C</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7480</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">100291056, 100291057, 100291058</t>
+          <t xml:space="preserve">4505435</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -14835,21 +14835,21 @@
         </is>
       </c>
       <c r="J198">
-        <v>11483</v>
+        <v>74</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311532840</t>
+          <t xml:space="preserve">311539389</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scanenergi A/S</t>
+          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-01</t>
+          <t xml:space="preserve">2031-08-06</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14891,17 +14891,17 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 1</t>
+          <t xml:space="preserve">Brorsonsvej 4</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">6933</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">4433294</t>
+          <t xml:space="preserve">5706491</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -14910,11 +14910,11 @@
         </is>
       </c>
       <c r="J199">
-        <v>324</v>
+        <v>4954</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311535258</t>
+          <t xml:space="preserve">311543939</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-12</t>
+          <t xml:space="preserve">2031-08-27</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14966,17 +14966,17 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkepladsen 1B</t>
+          <t xml:space="preserve">Brorsonsvej 2</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">6933</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">4455488</t>
+          <t xml:space="preserve">5706423</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -14985,11 +14985,11 @@
         </is>
       </c>
       <c r="J200">
-        <v>190</v>
+        <v>9030</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311535252</t>
+          <t xml:space="preserve">311547312</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -14999,7 +14999,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-07-12</t>
+          <t xml:space="preserve">2031-09-10</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -15041,30 +15041,30 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Burgårdsvej 8</t>
+          <t xml:space="preserve">Brorsonsvej 2</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">7480</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">4462912</t>
+          <t xml:space="preserve">5706423</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J201">
-        <v>848</v>
+        <v>802</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539387</t>
+          <t xml:space="preserve">311548281</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -15074,7 +15074,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-06</t>
+          <t xml:space="preserve">2031-09-15</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Røddingvej 21C</t>
+          <t xml:space="preserve">Midgaardsvej 20</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -15126,7 +15126,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">4505435</t>
+          <t xml:space="preserve">8748212</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -15135,11 +15135,11 @@
         </is>
       </c>
       <c r="J202">
-        <v>74</v>
+        <v>185</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311539389</t>
+          <t xml:space="preserve">311549309</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-06</t>
+          <t xml:space="preserve">2031-09-20</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -15191,30 +15191,30 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brorsonsvej 4</t>
+          <t xml:space="preserve">Midgaardsvej 20</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7480</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">5706491</t>
+          <t xml:space="preserve">8748212</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J203">
-        <v>4954</v>
+        <v>320</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311543939</t>
+          <t xml:space="preserve">311549309</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -15224,7 +15224,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-27</t>
+          <t xml:space="preserve">2031-09-20</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -15266,17 +15266,17 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brorsonsvej 2</t>
+          <t xml:space="preserve">Fuglsangsvej 15</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7480</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">5706423</t>
+          <t xml:space="preserve">739998, 4503192</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -15285,21 +15285,21 @@
         </is>
       </c>
       <c r="J204">
-        <v>9030</v>
+        <v>369</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311547312</t>
+          <t xml:space="preserve">311553193</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+          <t xml:space="preserve">Graugaard Consult aps</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-10</t>
+          <t xml:space="preserve">2031-10-05</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -15341,7 +15341,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brorsonsvej 2</t>
+          <t xml:space="preserve">Valeursvej 11</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -15351,20 +15351,20 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">5706423</t>
+          <t xml:space="preserve">5704408</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J205">
-        <v>802</v>
+        <v>1491</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311548281</t>
+          <t xml:space="preserve">311553355</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -15374,7 +15374,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-15</t>
+          <t xml:space="preserve">2031-10-06</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -15416,40 +15416,40 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midgaardsvej 20</t>
+          <t xml:space="preserve">Brændgårdvej 103C</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">7480</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">8748212</t>
+          <t xml:space="preserve">9868104</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="J206">
-        <v>185</v>
+        <v>269</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549309</t>
+          <t xml:space="preserve">311554956</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+          <t xml:space="preserve">EnergiTjenesten</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-20</t>
+          <t xml:space="preserve">2031-10-13</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -15491,40 +15491,40 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Midgaardsvej 20</t>
+          <t xml:space="preserve">Fyrrevej 8</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t xml:space="preserve">7480</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">8748212</t>
+          <t xml:space="preserve">5701206</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J207">
-        <v>320</v>
+        <v>400</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549309</t>
+          <t xml:space="preserve">311555699</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+          <t xml:space="preserve">EnergiTjenesten</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-20</t>
+          <t xml:space="preserve">2031-10-15</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -15566,40 +15566,40 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglsangsvej 15</t>
+          <t xml:space="preserve">Lyngens Kvarter 225</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t xml:space="preserve">7480</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">739998, 4503192</t>
+          <t xml:space="preserve">8966751</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J208">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t xml:space="preserve">311553193</t>
+          <t xml:space="preserve">311555700</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Graugaard Consult aps</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-05</t>
+          <t xml:space="preserve">2031-10-15</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15641,7 +15641,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valeursvej 11</t>
+          <t xml:space="preserve">Mørupvej 32</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -15651,7 +15651,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">5704408</t>
+          <t xml:space="preserve">5700249</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -15660,21 +15660,21 @@
         </is>
       </c>
       <c r="J209">
-        <v>1491</v>
+        <v>1238</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311553355</t>
+          <t xml:space="preserve">311555794</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten Jylland-Fyn</t>
+          <t xml:space="preserve">EnergiTjenesten</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-06</t>
+          <t xml:space="preserve">2031-10-15</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15716,7 +15716,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændgårdvej 103C</t>
+          <t xml:space="preserve">Snerlens Kvarter 11</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -15726,20 +15726,20 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">9868104</t>
+          <t xml:space="preserve">5700553</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J210">
-        <v>269</v>
+        <v>100</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311554956</t>
+          <t xml:space="preserve">311555701</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -15749,7 +15749,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-13</t>
+          <t xml:space="preserve">2031-10-15</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15791,17 +15791,17 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fyrrevej 8</t>
+          <t xml:space="preserve">Østre Søvej 2</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7451</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">5701206</t>
+          <t xml:space="preserve">4459086</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -15810,11 +15810,11 @@
         </is>
       </c>
       <c r="J211">
-        <v>400</v>
+        <v>304</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555695</t>
+          <t xml:space="preserve">311555714</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -15866,7 +15866,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lyngens Kvarter 225</t>
+          <t xml:space="preserve">Lindegårdsvej 10</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -15876,30 +15876,30 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">8966751</t>
+          <t xml:space="preserve">5699836</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J212">
-        <v>353</v>
+        <v>617</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555700</t>
+          <t xml:space="preserve">311559404</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">EnergiTjenesten</t>
         </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-15</t>
+          <t xml:space="preserve">2031-11-03</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15941,7 +15941,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mørupvej 32</t>
+          <t xml:space="preserve">Lindegårdsvej 10B</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -15951,7 +15951,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700249</t>
+          <t xml:space="preserve">5699836</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -15960,11 +15960,11 @@
         </is>
       </c>
       <c r="J213">
-        <v>1238</v>
+        <v>824</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555794</t>
+          <t xml:space="preserve">311559406</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-15</t>
+          <t xml:space="preserve">2031-11-03</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -16016,7 +16016,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snerlens Kvarter 11</t>
+          <t xml:space="preserve">Lindegårdsvej 146</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -16026,7 +16026,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700553</t>
+          <t xml:space="preserve">1809289</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -16035,11 +16035,11 @@
         </is>
       </c>
       <c r="J214">
-        <v>100</v>
+        <v>771</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555701</t>
+          <t xml:space="preserve">311560386</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -16049,7 +16049,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-15</t>
+          <t xml:space="preserve">2031-11-08</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -16091,30 +16091,30 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Søvej 2</t>
+          <t xml:space="preserve">Herluf Trolles Vej 1A</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t xml:space="preserve">7451</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">4459086</t>
+          <t xml:space="preserve">5699836</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J215">
-        <v>304</v>
+        <v>525</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t xml:space="preserve">311555714</t>
+          <t xml:space="preserve">311561966</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -16124,7 +16124,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-15</t>
+          <t xml:space="preserve">2031-11-15</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -16166,7 +16166,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindegårdsvej 10</t>
+          <t xml:space="preserve">Herluf Trolles Vej 1B</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -16181,15 +16181,15 @@
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="J216">
-        <v>617</v>
+        <v>522</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559404</t>
+          <t xml:space="preserve">311566877</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -16199,7 +16199,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-03</t>
+          <t xml:space="preserve">2031-11-15</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindegårdsvej 10B</t>
+          <t xml:space="preserve">Lindegårdsvej 6</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -16256,15 +16256,15 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="J217">
-        <v>824</v>
+        <v>802</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t xml:space="preserve">311559406</t>
+          <t xml:space="preserve">311561962</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -16274,7 +16274,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-03</t>
+          <t xml:space="preserve">2031-11-15</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindegårdsvej 146</t>
+          <t xml:space="preserve">Lindegårdsvej 8</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -16326,20 +16326,20 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t xml:space="preserve">1809289</t>
+          <t xml:space="preserve">5699836</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">20</t>
         </is>
       </c>
       <c r="J218">
-        <v>771</v>
+        <v>472</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t xml:space="preserve">311560386</t>
+          <t xml:space="preserve">311561963</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -16349,7 +16349,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-08</t>
+          <t xml:space="preserve">2031-11-15</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -16391,7 +16391,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herluf Trolles Vej 1A</t>
+          <t xml:space="preserve">Bryggergade 7A</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -16401,20 +16401,20 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699836</t>
+          <t xml:space="preserve">5697449</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J219">
-        <v>525</v>
+        <v>229</v>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561966</t>
+          <t xml:space="preserve">311566223</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -16424,7 +16424,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-15</t>
+          <t xml:space="preserve">2031-12-06</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -16466,7 +16466,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herluf Trolles Vej 1B</t>
+          <t xml:space="preserve">Bryggergade 7A</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -16476,20 +16476,20 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699836</t>
+          <t xml:space="preserve">5697449</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">17</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J220">
-        <v>522</v>
+        <v>70</v>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566877</t>
+          <t xml:space="preserve">311566228</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-15</t>
+          <t xml:space="preserve">2031-12-06</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -16541,7 +16541,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindegårdsvej 6</t>
+          <t xml:space="preserve">Kaj Zartows Vej 19</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -16551,20 +16551,20 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699836</t>
+          <t xml:space="preserve">8966321</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J221">
-        <v>802</v>
+        <v>615</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561962</t>
+          <t xml:space="preserve">311566234</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -16574,7 +16574,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-15</t>
+          <t xml:space="preserve">2031-12-06</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -16616,30 +16616,30 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindegårdsvej 8</t>
+          <t xml:space="preserve">Kastanie Alle 27</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">6933</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699836</t>
+          <t xml:space="preserve">9455731</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J222">
-        <v>472</v>
+        <v>1001</v>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t xml:space="preserve">311561963</t>
+          <t xml:space="preserve">311566808</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -16649,7 +16649,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-15</t>
+          <t xml:space="preserve">2031-12-08</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16691,7 +16691,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bryggergade 7A</t>
+          <t xml:space="preserve">Nørregade 7A</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -16701,30 +16701,30 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">5697449</t>
+          <t xml:space="preserve">7168779</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J223">
-        <v>229</v>
+        <v>64</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566223</t>
+          <t xml:space="preserve">311566779</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten</t>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-06</t>
+          <t xml:space="preserve">2031-12-08</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16766,7 +16766,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bryggergade 7A</t>
+          <t xml:space="preserve">Vesterlindvej 21</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -16776,20 +16776,20 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">5697449</t>
+          <t xml:space="preserve">4452247</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J224">
-        <v>70</v>
+        <v>430</v>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566228</t>
+          <t xml:space="preserve">311567053</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -16799,7 +16799,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-06</t>
+          <t xml:space="preserve">2031-12-09</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16841,30 +16841,30 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaj Zartows Vej 19</t>
+          <t xml:space="preserve">Solbakken 30A</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">6933</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">8966321</t>
+          <t xml:space="preserve">4433142</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J225">
-        <v>615</v>
+        <v>2469</v>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566234</t>
+          <t xml:space="preserve">311568010</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -16874,7 +16874,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-06</t>
+          <t xml:space="preserve">2031-12-15</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16916,17 +16916,17 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastanie Alle 27</t>
+          <t xml:space="preserve">Østergade 5</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t xml:space="preserve">6933</t>
+          <t xml:space="preserve">7490</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">9455731</t>
+          <t xml:space="preserve">4433876</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -16935,11 +16935,11 @@
         </is>
       </c>
       <c r="J226">
-        <v>1001</v>
+        <v>2190</v>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566808</t>
+          <t xml:space="preserve">311568091</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -16949,7 +16949,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-08</t>
+          <t xml:space="preserve">2031-12-15</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16991,7 +16991,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 7A</t>
+          <t xml:space="preserve">Vestergade 82</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -17001,30 +17001,30 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">7168779</t>
+          <t xml:space="preserve">5699393</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J227">
-        <v>64</v>
+        <v>626</v>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311566779</t>
+          <t xml:space="preserve">311568880</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve">EnergiTjenesten</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-08</t>
+          <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -17066,30 +17066,30 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterlindvej 21</t>
+          <t xml:space="preserve">Ågårdsvej 2D</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7480</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">4452247</t>
+          <t xml:space="preserve">9888291</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J228">
-        <v>430</v>
+        <v>948</v>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t xml:space="preserve">311567053</t>
+          <t xml:space="preserve">311568878</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -17099,7 +17099,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-09</t>
+          <t xml:space="preserve">2031-12-20</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -17141,7 +17141,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Haugevej 25</t>
+          <t xml:space="preserve">Dueoddevej 9</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -17151,7 +17151,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">100063131</t>
+          <t xml:space="preserve">5705804</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -17160,11 +17160,11 @@
         </is>
       </c>
       <c r="J229">
-        <v>1683</v>
+        <v>1962</v>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t xml:space="preserve">311567248</t>
+          <t xml:space="preserve">311571890</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -17174,7 +17174,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-10</t>
+          <t xml:space="preserve">2032-01-12</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -17216,30 +17216,30 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solbakken 30A</t>
+          <t xml:space="preserve">Brændgårdvej 99</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t xml:space="preserve">6933</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">4433142</t>
+          <t xml:space="preserve">8481827</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J230">
-        <v>2469</v>
+        <v>77</v>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568010</t>
+          <t xml:space="preserve">311572664</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -17249,7 +17249,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-15</t>
+          <t xml:space="preserve">2032-01-17</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -17291,30 +17291,30 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 5</t>
+          <t xml:space="preserve">Brændgårdvej 99</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t xml:space="preserve">7490</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t xml:space="preserve">4433876</t>
+          <t xml:space="preserve">8481827</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J231">
-        <v>2190</v>
+        <v>550</v>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568091</t>
+          <t xml:space="preserve">311572663</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -17324,7 +17324,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-15</t>
+          <t xml:space="preserve">2032-01-17</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -17366,7 +17366,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 82</t>
+          <t xml:space="preserve">Ringkøbingvej 112</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -17376,7 +17376,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699393</t>
+          <t xml:space="preserve">100002469</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -17385,11 +17385,11 @@
         </is>
       </c>
       <c r="J232">
-        <v>626</v>
+        <v>2608</v>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568880</t>
+          <t xml:space="preserve">311574347</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -17399,7 +17399,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-20</t>
+          <t xml:space="preserve">2032-01-25</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -17441,17 +17441,17 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ågårdsvej 2D</t>
+          <t xml:space="preserve">Gisselfeldvej 2</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t xml:space="preserve">7480</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t xml:space="preserve">9888291</t>
+          <t xml:space="preserve">5708304</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -17460,11 +17460,11 @@
         </is>
       </c>
       <c r="J233">
-        <v>948</v>
+        <v>1303</v>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t xml:space="preserve">311568878</t>
+          <t xml:space="preserve">311575936</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -17474,7 +17474,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-20</t>
+          <t xml:space="preserve">2032-02-01</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -17516,7 +17516,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dueoddevej 9</t>
+          <t xml:space="preserve">Gisselfeldvej 2</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -17526,20 +17526,20 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">5705804</t>
+          <t xml:space="preserve">5708304</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J234">
-        <v>1962</v>
+        <v>305</v>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t xml:space="preserve">311571890</t>
+          <t xml:space="preserve">311575938</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -17549,7 +17549,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-12</t>
+          <t xml:space="preserve">2032-02-01</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -17591,7 +17591,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændgårdvej 99</t>
+          <t xml:space="preserve">Gyvelens Kvarter 10</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -17601,20 +17601,20 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t xml:space="preserve">8481827</t>
+          <t xml:space="preserve">8966750</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J235">
-        <v>77</v>
+        <v>400</v>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t xml:space="preserve">311572664</t>
+          <t xml:space="preserve">311575933</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -17624,7 +17624,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-17</t>
+          <t xml:space="preserve">2032-02-01</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -17666,7 +17666,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændgårdvej 99</t>
+          <t xml:space="preserve">Skovvænget 2B</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -17676,20 +17676,20 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">8481827</t>
+          <t xml:space="preserve">9827058</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J236">
-        <v>550</v>
+        <v>825</v>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t xml:space="preserve">311572663</t>
+          <t xml:space="preserve">311575940</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -17699,7 +17699,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-17</t>
+          <t xml:space="preserve">2032-02-01</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17741,7 +17741,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringkøbingvej 112</t>
+          <t xml:space="preserve">Museumsgade 32</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -17751,7 +17751,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">100002469</t>
+          <t xml:space="preserve">5700031</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -17760,11 +17760,11 @@
         </is>
       </c>
       <c r="J237">
-        <v>2608</v>
+        <v>2327</v>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311574347</t>
+          <t xml:space="preserve">311577008</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -17774,7 +17774,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-01-25</t>
+          <t xml:space="preserve">2032-02-06</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gisselfeldvej 2</t>
+          <t xml:space="preserve">Skovvænget 2A</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -17826,20 +17826,20 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">5708304</t>
+          <t xml:space="preserve">9827058</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J238">
-        <v>1303</v>
+        <v>514</v>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t xml:space="preserve">311575936</t>
+          <t xml:space="preserve">311577005</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -17849,7 +17849,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-01</t>
+          <t xml:space="preserve">2032-02-06</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17891,7 +17891,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gisselfeldvej 2</t>
+          <t xml:space="preserve">Brændgårdvej 107</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -17901,20 +17901,20 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">5708304</t>
+          <t xml:space="preserve">100377971</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J239">
-        <v>305</v>
+        <v>9582</v>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t xml:space="preserve">311575938</t>
+          <t xml:space="preserve">311582020</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -17924,7 +17924,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-01</t>
+          <t xml:space="preserve">2032-03-02</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17966,7 +17966,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyvelens Kvarter 10</t>
+          <t xml:space="preserve">Brændgårdvej 20B</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -17976,20 +17976,20 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">8966750</t>
+          <t xml:space="preserve">5706289</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J240">
-        <v>400</v>
+        <v>3371</v>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t xml:space="preserve">311575933</t>
+          <t xml:space="preserve">311582023</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -17999,7 +17999,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-01</t>
+          <t xml:space="preserve">2032-03-02</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -18041,7 +18041,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvænget 2B</t>
+          <t xml:space="preserve">Brændgårdvej 99</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -18051,20 +18051,20 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t xml:space="preserve">9827058</t>
+          <t xml:space="preserve">8481827</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J241">
-        <v>825</v>
+        <v>478</v>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t xml:space="preserve">311575940</t>
+          <t xml:space="preserve">311582021</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-01</t>
+          <t xml:space="preserve">2032-03-02</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -18116,7 +18116,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Museumsgade 32</t>
+          <t xml:space="preserve">Brændgårdvej 99</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -18126,20 +18126,20 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700031</t>
+          <t xml:space="preserve">8481827</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J242">
-        <v>2327</v>
+        <v>453</v>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t xml:space="preserve">311577008</t>
+          <t xml:space="preserve">311582022</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -18149,7 +18149,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-06</t>
+          <t xml:space="preserve">2032-03-02</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -18191,7 +18191,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvænget 2A</t>
+          <t xml:space="preserve">Brændgårdvej 99</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -18201,20 +18201,20 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">9827058</t>
+          <t xml:space="preserve">8481827</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J243">
-        <v>514</v>
+        <v>130</v>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t xml:space="preserve">311577005</t>
+          <t xml:space="preserve">311582022</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -18224,7 +18224,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-02-06</t>
+          <t xml:space="preserve">2032-03-02</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -18266,7 +18266,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændgårdvej 107</t>
+          <t xml:space="preserve">Dalgas Plads 7A</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -18276,30 +18276,30 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t xml:space="preserve">100377971</t>
+          <t xml:space="preserve">334005, 334006, 334007, 334008, 334009, 334010, 334011, 334012, 334013, 334014, 334015, 334016, 334017, 334018, 334019, 334020, 334021, 334022, 334023, 334024, 334025, 334026, 334027, 334028, 334029, 334030, 334036, 334031, 334032, 334033, 334034, 334035, 334037, 334038, 334039, 334040, 334042, 100319954</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J244">
-        <v>9582</v>
+        <v>9740</v>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582020</t>
+          <t xml:space="preserve">311586771</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten</t>
+          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-02</t>
+          <t xml:space="preserve">2032-03-21</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -18341,7 +18341,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændgårdvej 20B</t>
+          <t xml:space="preserve">Birk Centerpark 1</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -18351,20 +18351,20 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t xml:space="preserve">5706289</t>
+          <t xml:space="preserve">4439896</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J245">
-        <v>3371</v>
+        <v>706</v>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582023</t>
+          <t xml:space="preserve">311587481</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -18374,7 +18374,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-02</t>
+          <t xml:space="preserve">2032-03-23</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -18416,7 +18416,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændgårdvej 99</t>
+          <t xml:space="preserve">Valdemarsvej 349</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -18426,20 +18426,20 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">8481827</t>
+          <t xml:space="preserve">5704898</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J246">
-        <v>478</v>
+        <v>176</v>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582021</t>
+          <t xml:space="preserve">311587770</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -18449,7 +18449,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-02</t>
+          <t xml:space="preserve">2032-03-24</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -18491,7 +18491,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændgårdvej 99</t>
+          <t xml:space="preserve">Valdemarsvej 359</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -18501,20 +18501,20 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t xml:space="preserve">8481827</t>
+          <t xml:space="preserve">5704898</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J247">
-        <v>453</v>
+        <v>787</v>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582022</t>
+          <t xml:space="preserve">311587769</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -18524,7 +18524,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-02</t>
+          <t xml:space="preserve">2032-03-24</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -18566,30 +18566,30 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brændgårdvej 99</t>
+          <t xml:space="preserve">Velhustedvej 12B</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">6933</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">8481827</t>
+          <t xml:space="preserve">1805364</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J248">
-        <v>130</v>
+        <v>340</v>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582022</t>
+          <t xml:space="preserve">311587772</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -18599,7 +18599,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-02</t>
+          <t xml:space="preserve">2032-03-24</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -18641,7 +18641,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dalgas Plads 7A</t>
+          <t xml:space="preserve">Engbjerg 21</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -18651,30 +18651,30 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">334005, 334006, 334007, 334008, 334009, 334010, 334011, 334012, 334013, 334014, 334015, 334016, 334017, 334018, 334019, 334020, 334021, 334022, 334023, 334024, 334025, 334026, 334027, 334028, 334029, 334030, 334036, 334031, 334032, 334033, 334034, 334035, 334037, 334038, 334039, 334040, 334042, 100319954</t>
+          <t xml:space="preserve">4456901</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J249">
-        <v>9740</v>
+        <v>625</v>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586771</t>
+          <t xml:space="preserve">311588514</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t xml:space="preserve">GH-Energi &amp; Rådgivning ApS</t>
+          <t xml:space="preserve">EnergiTjenesten</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-21</t>
+          <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -18716,7 +18716,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birk Centerpark 1</t>
+          <t xml:space="preserve">Engbjerg 23</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -18726,20 +18726,20 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">4439896</t>
+          <t xml:space="preserve">4456901</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J250">
-        <v>706</v>
+        <v>738</v>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t xml:space="preserve">311587481</t>
+          <t xml:space="preserve">311588517</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -18749,7 +18749,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-23</t>
+          <t xml:space="preserve">2032-03-28</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18791,7 +18791,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdemarsvej 349</t>
+          <t xml:space="preserve">Nørregade 30</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -18801,20 +18801,20 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">5704898</t>
+          <t xml:space="preserve">7268351</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J251">
-        <v>176</v>
+        <v>6466</v>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t xml:space="preserve">311587770</t>
+          <t xml:space="preserve">311596592</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -18824,7 +18824,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-24</t>
+          <t xml:space="preserve">2032-04-29</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18866,7 +18866,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdemarsvej 359</t>
+          <t xml:space="preserve">Snerlens Kvarter 13</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -18876,20 +18876,20 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">5704898</t>
+          <t xml:space="preserve">5700553</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J252">
-        <v>787</v>
+        <v>120</v>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t xml:space="preserve">311587769</t>
+          <t xml:space="preserve">311596585</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -18899,7 +18899,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-24</t>
+          <t xml:space="preserve">2032-04-29</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18941,30 +18941,30 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Velhustedvej 12B</t>
+          <t xml:space="preserve">Vistorpvej 26</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t xml:space="preserve">6933</t>
+          <t xml:space="preserve">7540</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805364</t>
+          <t xml:space="preserve">4508718</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J253">
-        <v>340</v>
+        <v>139</v>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t xml:space="preserve">311587772</t>
+          <t xml:space="preserve">311596586</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -18974,7 +18974,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-24</t>
+          <t xml:space="preserve">2032-04-29</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -19016,30 +19016,30 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engbjerg 21</t>
+          <t xml:space="preserve">Vistorpvej 26</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7540</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">4456901</t>
+          <t xml:space="preserve">4508718</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J254">
-        <v>625</v>
+        <v>79</v>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588514</t>
+          <t xml:space="preserve">311596589</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -19049,7 +19049,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-28</t>
+          <t xml:space="preserve">2032-04-29</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -19091,7 +19091,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Engbjerg 23</t>
+          <t xml:space="preserve">Ørre Byvej 83</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -19101,20 +19101,20 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">4456901</t>
+          <t xml:space="preserve">4464883</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J255">
-        <v>738</v>
+        <v>176</v>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t xml:space="preserve">311588517</t>
+          <t xml:space="preserve">311596583</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -19124,7 +19124,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-28</t>
+          <t xml:space="preserve">2032-04-29</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -19166,30 +19166,30 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 30</t>
+          <t xml:space="preserve">Birkmosevej 26</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7480</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t xml:space="preserve">7268351</t>
+          <t xml:space="preserve">4503146</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J256">
-        <v>6466</v>
+        <v>347</v>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t xml:space="preserve">311596592</t>
+          <t xml:space="preserve">311598021</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -19199,7 +19199,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-29</t>
+          <t xml:space="preserve">2032-05-05</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -19241,30 +19241,30 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snerlens Kvarter 13</t>
+          <t xml:space="preserve">Skolegade 4</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7550</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700553</t>
+          <t xml:space="preserve">4505959</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J257">
-        <v>120</v>
+        <v>244</v>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t xml:space="preserve">311596585</t>
+          <t xml:space="preserve">311598022</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -19274,7 +19274,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-29</t>
+          <t xml:space="preserve">2032-05-05</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -19316,17 +19316,17 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vistorpvej 26</t>
+          <t xml:space="preserve">Valdemarsvej 343</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t xml:space="preserve">7540</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">4508718</t>
+          <t xml:space="preserve">5704898</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -19335,11 +19335,11 @@
         </is>
       </c>
       <c r="J258">
-        <v>139</v>
+        <v>15574</v>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311596586</t>
+          <t xml:space="preserve">311598704</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -19349,7 +19349,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-29</t>
+          <t xml:space="preserve">2032-05-09</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -19391,30 +19391,30 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vistorpvej 26</t>
+          <t xml:space="preserve">Sandagervej 35</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t xml:space="preserve">7540</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t xml:space="preserve">4508718</t>
+          <t xml:space="preserve">5700242</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J259">
-        <v>79</v>
+        <v>904</v>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t xml:space="preserve">311596589</t>
+          <t xml:space="preserve">311599479</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -19424,7 +19424,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-29</t>
+          <t xml:space="preserve">2032-05-11</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -19466,7 +19466,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørre Byvej 83</t>
+          <t xml:space="preserve">Fenrisvej 24</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
@@ -19476,20 +19476,20 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">4464883</t>
+          <t xml:space="preserve">5702325</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J260">
-        <v>176</v>
+        <v>280</v>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t xml:space="preserve">311596583</t>
+          <t xml:space="preserve">311601100</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -19499,7 +19499,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-29</t>
+          <t xml:space="preserve">2032-05-18</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -19541,30 +19541,30 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkmosevej 26</t>
+          <t xml:space="preserve">Nørregade 11A</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t xml:space="preserve">7480</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">4503146</t>
+          <t xml:space="preserve">5697089</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J261">
-        <v>347</v>
+        <v>1066</v>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t xml:space="preserve">311598021</t>
+          <t xml:space="preserve">311601096</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -19574,7 +19574,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-05</t>
+          <t xml:space="preserve">2032-05-18</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -19616,17 +19616,17 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 4</t>
+          <t xml:space="preserve">Vestergade 100A</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t xml:space="preserve">7550</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">4505959</t>
+          <t xml:space="preserve">5699206</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -19635,11 +19635,11 @@
         </is>
       </c>
       <c r="J262">
-        <v>244</v>
+        <v>78</v>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311598022</t>
+          <t xml:space="preserve">311601105</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -19649,7 +19649,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-05</t>
+          <t xml:space="preserve">2032-05-18</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -19691,7 +19691,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Valdemarsvej 343</t>
+          <t xml:space="preserve">Vestergade 100B</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
@@ -19701,20 +19701,20 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">5704898</t>
+          <t xml:space="preserve">5699206</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J263">
-        <v>15574</v>
+        <v>78</v>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t xml:space="preserve">311598704</t>
+          <t xml:space="preserve">311601107</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -19724,7 +19724,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-09</t>
+          <t xml:space="preserve">2032-05-18</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -19766,7 +19766,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandagervej 35</t>
+          <t xml:space="preserve">Vestergade 100C</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
@@ -19776,20 +19776,20 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700242</t>
+          <t xml:space="preserve">5699206</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J264">
-        <v>904</v>
+        <v>78</v>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t xml:space="preserve">311599479</t>
+          <t xml:space="preserve">311601109</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
@@ -19799,7 +19799,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-11</t>
+          <t xml:space="preserve">2032-05-18</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -19841,7 +19841,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fenrisvej 24</t>
+          <t xml:space="preserve">Vestergade 100D</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
@@ -19851,20 +19851,20 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t xml:space="preserve">5702325</t>
+          <t xml:space="preserve">5699206</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J265">
-        <v>280</v>
+        <v>78</v>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601100</t>
+          <t xml:space="preserve">311601110</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -19916,7 +19916,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 11A</t>
+          <t xml:space="preserve">Vestergade 100E</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -19926,20 +19926,20 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">5697089</t>
+          <t xml:space="preserve">5699206</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J266">
-        <v>1066</v>
+        <v>78</v>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601096</t>
+          <t xml:space="preserve">311601111</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -19991,7 +19991,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 100A</t>
+          <t xml:space="preserve">Vestergade 100F</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -20006,7 +20006,7 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J267">
@@ -20014,7 +20014,7 @@
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601105</t>
+          <t xml:space="preserve">311601117</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -20066,7 +20066,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 100B</t>
+          <t xml:space="preserve">Vestergade 100G</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
@@ -20081,7 +20081,7 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J268">
@@ -20089,7 +20089,7 @@
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601107</t>
+          <t xml:space="preserve">311601118</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -20141,7 +20141,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 100C</t>
+          <t xml:space="preserve">Vestergade 100H</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
@@ -20156,7 +20156,7 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J269">
@@ -20164,7 +20164,7 @@
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601109</t>
+          <t xml:space="preserve">311601120</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -20216,7 +20216,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 100D</t>
+          <t xml:space="preserve">Vestergade 100I</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
@@ -20231,7 +20231,7 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J270">
@@ -20239,7 +20239,7 @@
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601110</t>
+          <t xml:space="preserve">311601121</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -20291,7 +20291,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 100E</t>
+          <t xml:space="preserve">Vestergade 100K</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
@@ -20306,7 +20306,7 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J271">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601111</t>
+          <t xml:space="preserve">311601122</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -20366,7 +20366,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 100F</t>
+          <t xml:space="preserve">Vestergade 100L</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
@@ -20381,7 +20381,7 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J272">
@@ -20389,7 +20389,7 @@
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601117</t>
+          <t xml:space="preserve">311601124</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -20441,7 +20441,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 100G</t>
+          <t xml:space="preserve">Vestergade 100M</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
@@ -20456,7 +20456,7 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J273">
@@ -20464,7 +20464,7 @@
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601118</t>
+          <t xml:space="preserve">311601127</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -20516,7 +20516,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 100H</t>
+          <t xml:space="preserve">Gl. Skolevej 76</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -20526,20 +20526,20 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699206</t>
+          <t xml:space="preserve">5699373</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J274">
-        <v>78</v>
+        <v>1547</v>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601120</t>
+          <t xml:space="preserve">311604976</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -20549,7 +20549,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-18</t>
+          <t xml:space="preserve">2032-06-02</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -20591,7 +20591,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 100I</t>
+          <t xml:space="preserve">Bethaniagade 3A</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
@@ -20601,20 +20601,20 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699206</t>
+          <t xml:space="preserve">5697356</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J275">
-        <v>78</v>
+        <v>365</v>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601121</t>
+          <t xml:space="preserve">311605257</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -20624,7 +20624,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-18</t>
+          <t xml:space="preserve">2032-06-03</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -20666,7 +20666,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 100K</t>
+          <t xml:space="preserve">Brorsonsvej 12</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
@@ -20676,20 +20676,20 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699206</t>
+          <t xml:space="preserve">5706488</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J276">
-        <v>78</v>
+        <v>2761</v>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601122</t>
+          <t xml:space="preserve">311613717</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -20699,7 +20699,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-18</t>
+          <t xml:space="preserve">2032-07-07</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -20741,7 +20741,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 100L</t>
+          <t xml:space="preserve">Brorsonsvej 14</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
@@ -20751,20 +20751,20 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699206</t>
+          <t xml:space="preserve">5706488</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J277">
-        <v>78</v>
+        <v>1280</v>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601124</t>
+          <t xml:space="preserve">311613723</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -20774,7 +20774,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-18</t>
+          <t xml:space="preserve">2032-07-07</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -20816,7 +20816,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 100M</t>
+          <t xml:space="preserve">Brorsonsvej 16</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
@@ -20826,20 +20826,20 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699206</t>
+          <t xml:space="preserve">5706488</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J278">
-        <v>78</v>
+        <v>1280</v>
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t xml:space="preserve">311601127</t>
+          <t xml:space="preserve">311613722</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
@@ -20849,7 +20849,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-05-18</t>
+          <t xml:space="preserve">2032-07-07</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -20891,7 +20891,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Skolevej 76</t>
+          <t xml:space="preserve">Brorsonsvej 18</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
@@ -20901,20 +20901,20 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699373</t>
+          <t xml:space="preserve">5706488</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J279">
-        <v>1547</v>
+        <v>1280</v>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t xml:space="preserve">311604976</t>
+          <t xml:space="preserve">311613720</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
@@ -20924,7 +20924,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-02</t>
+          <t xml:space="preserve">2032-07-07</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20966,7 +20966,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bethaniagade 3A</t>
+          <t xml:space="preserve">Rosenholmvej 29</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
@@ -20976,20 +20976,20 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t xml:space="preserve">5697356</t>
+          <t xml:space="preserve">9874254</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J280">
-        <v>365</v>
+        <v>1070</v>
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t xml:space="preserve">311605257</t>
+          <t xml:space="preserve">311613998</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
@@ -20999,7 +20999,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-06-03</t>
+          <t xml:space="preserve">2032-07-08</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -21041,7 +21041,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brorsonsvej 12</t>
+          <t xml:space="preserve">Rosenholmvej 33</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
@@ -21051,20 +21051,20 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t xml:space="preserve">5706488</t>
+          <t xml:space="preserve">9874254</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J281">
-        <v>2761</v>
+        <v>1084</v>
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t xml:space="preserve">311613717</t>
+          <t xml:space="preserve">311614001</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
@@ -21074,7 +21074,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-07</t>
+          <t xml:space="preserve">2032-07-08</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -21116,7 +21116,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brorsonsvej 14</t>
+          <t xml:space="preserve">Rosenholmvej 35</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
@@ -21126,20 +21126,20 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t xml:space="preserve">5706488</t>
+          <t xml:space="preserve">9874254</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J282">
-        <v>1280</v>
+        <v>2879</v>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t xml:space="preserve">311613723</t>
+          <t xml:space="preserve">311614000</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -21149,7 +21149,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-07</t>
+          <t xml:space="preserve">2032-07-08</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -21191,7 +21191,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brorsonsvej 16</t>
+          <t xml:space="preserve">Bethaniagade 3B</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
@@ -21201,20 +21201,20 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t xml:space="preserve">5706488</t>
+          <t xml:space="preserve">5697356</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J283">
-        <v>1280</v>
+        <v>1048</v>
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t xml:space="preserve">311613722</t>
+          <t xml:space="preserve">311620382</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-07</t>
+          <t xml:space="preserve">2032-08-15</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -21266,30 +21266,30 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brorsonsvej 18</t>
+          <t xml:space="preserve">Fuglevænget 1</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7480</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t xml:space="preserve">5706488</t>
+          <t xml:space="preserve">4503146</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J284">
-        <v>1280</v>
+        <v>957</v>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t xml:space="preserve">311613720</t>
+          <t xml:space="preserve">311620387</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
@@ -21299,7 +21299,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-07</t>
+          <t xml:space="preserve">2032-08-15</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -21341,30 +21341,30 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenholmvej 29</t>
+          <t xml:space="preserve">Fuglevænget 1</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7480</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">9874254</t>
+          <t xml:space="preserve">4503146</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J285">
-        <v>1070</v>
+        <v>927</v>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t xml:space="preserve">311613998</t>
+          <t xml:space="preserve">311620389</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
@@ -21374,7 +21374,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-08</t>
+          <t xml:space="preserve">2032-08-15</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -21401,12 +21401,12 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herning Kommune</t>
+          <t xml:space="preserve">bomidtvest</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
@@ -21416,7 +21416,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenholmvej 33</t>
+          <t xml:space="preserve">Bytoften 79</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
@@ -21426,30 +21426,30 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">9874254</t>
+          <t xml:space="preserve">331825, 331826</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J286">
-        <v>1084</v>
+        <v>781</v>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t xml:space="preserve">311614001</t>
+          <t xml:space="preserve">311622284</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-08</t>
+          <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -21491,7 +21491,7 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenholmvej 35</t>
+          <t xml:space="preserve">Skoletoften 7</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
@@ -21501,7 +21501,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">9874254</t>
+          <t xml:space="preserve">4455105</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -21510,11 +21510,11 @@
         </is>
       </c>
       <c r="J287">
-        <v>2879</v>
+        <v>1524</v>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t xml:space="preserve">311614000</t>
+          <t xml:space="preserve">311622235</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -21524,7 +21524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-08</t>
+          <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -21566,7 +21566,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bethaniagade 3B</t>
+          <t xml:space="preserve">Skoletoften 7</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
@@ -21576,20 +21576,20 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">5697356</t>
+          <t xml:space="preserve">4455105</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J288">
-        <v>1048</v>
+        <v>1719</v>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620382</t>
+          <t xml:space="preserve">311622236</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
@@ -21599,7 +21599,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-15</t>
+          <t xml:space="preserve">2032-08-23</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -21641,17 +21641,17 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglevænget 1</t>
+          <t xml:space="preserve">Nøvlingvej 8</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t xml:space="preserve">7480</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">4503146</t>
+          <t xml:space="preserve">4455094</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -21660,11 +21660,11 @@
         </is>
       </c>
       <c r="J289">
-        <v>957</v>
+        <v>138</v>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620387</t>
+          <t xml:space="preserve">311623320</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
@@ -21674,7 +21674,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-15</t>
+          <t xml:space="preserve">2032-08-26</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -21716,30 +21716,30 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglevænget 1</t>
+          <t xml:space="preserve">Th. Nielsens Gade 25</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t xml:space="preserve">7480</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t xml:space="preserve">4503146</t>
+          <t xml:space="preserve">5696550</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J290">
-        <v>927</v>
+        <v>653</v>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620389</t>
+          <t xml:space="preserve">311623523</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
@@ -21749,7 +21749,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-15</t>
+          <t xml:space="preserve">2032-08-26</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -21776,12 +21776,12 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t xml:space="preserve">bomidtvest</t>
+          <t xml:space="preserve">Herning Kommune</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -21791,17 +21791,17 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bytoften 79</t>
+          <t xml:space="preserve">Langgade 16</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7550</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">331825, 331826</t>
+          <t xml:space="preserve">334871, 334872</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -21810,11 +21810,11 @@
         </is>
       </c>
       <c r="J291">
-        <v>781</v>
+        <v>2108</v>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622284</t>
+          <t xml:space="preserve">311623871</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
@@ -21824,7 +21824,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-23</t>
+          <t xml:space="preserve">2032-08-29</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -21866,7 +21866,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skoletoften 7</t>
+          <t xml:space="preserve">Gilmosevej 20</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -21876,20 +21876,20 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">4455105</t>
+          <t xml:space="preserve">5707304</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J292">
-        <v>1524</v>
+        <v>8928</v>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622235</t>
+          <t xml:space="preserve">311628842</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
@@ -21899,7 +21899,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-23</t>
+          <t xml:space="preserve">2032-09-19</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -21941,7 +21941,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skoletoften 7</t>
+          <t xml:space="preserve">Baunetoften 101</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -21951,20 +21951,20 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">4455105</t>
+          <t xml:space="preserve">8279488</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J293">
-        <v>1719</v>
+        <v>860</v>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622236</t>
+          <t xml:space="preserve">311639214</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
@@ -21974,7 +21974,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-23</t>
+          <t xml:space="preserve">2032-10-31</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -22016,7 +22016,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nøvlingvej 8</t>
+          <t xml:space="preserve">Rosenholmvej 31</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
@@ -22026,20 +22026,20 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t xml:space="preserve">4455094</t>
+          <t xml:space="preserve">9874254</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J294">
-        <v>138</v>
+        <v>389</v>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t xml:space="preserve">311623320</t>
+          <t xml:space="preserve">311639215</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
@@ -22049,7 +22049,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-26</t>
+          <t xml:space="preserve">2032-10-31</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -22091,7 +22091,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Th. Nielsens Gade 25</t>
+          <t xml:space="preserve">Lindegårdsvej 3A</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
@@ -22101,20 +22101,20 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">5696550</t>
+          <t xml:space="preserve">5699861</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J295">
-        <v>653</v>
+        <v>2443</v>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t xml:space="preserve">311623523</t>
+          <t xml:space="preserve">311643464</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
@@ -22124,7 +22124,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-26</t>
+          <t xml:space="preserve">2032-11-18</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -22166,40 +22166,40 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langgade 16</t>
+          <t xml:space="preserve">Lindegårdsvej 3B</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t xml:space="preserve">7550</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t xml:space="preserve">334871, 334872</t>
+          <t xml:space="preserve">5699861</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J296">
-        <v>2108</v>
+        <v>1548</v>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t xml:space="preserve">311623871</t>
+          <t xml:space="preserve">311643474</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">EnergiTjenesten</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-29</t>
+          <t xml:space="preserve">2032-11-18</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -22241,7 +22241,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gilmosevej 20</t>
+          <t xml:space="preserve">Lindegårdsvej 3D</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
@@ -22251,20 +22251,20 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t xml:space="preserve">5707304</t>
+          <t xml:space="preserve">5699861</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J297">
-        <v>8928</v>
+        <v>2443</v>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t xml:space="preserve">311628842</t>
+          <t xml:space="preserve">311643467</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-19</t>
+          <t xml:space="preserve">2032-11-18</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -22316,7 +22316,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baunetoften 101</t>
+          <t xml:space="preserve">Lindegårdsvej 5</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
@@ -22326,20 +22326,20 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">8279488</t>
+          <t xml:space="preserve">5699861</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J298">
-        <v>860</v>
+        <v>2011</v>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t xml:space="preserve">311639214</t>
+          <t xml:space="preserve">311643469</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
@@ -22349,7 +22349,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-31</t>
+          <t xml:space="preserve">2032-11-18</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -22391,7 +22391,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenholmvej 31</t>
+          <t xml:space="preserve">Søbysøvej 7</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
@@ -22401,20 +22401,20 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">9874254</t>
+          <t xml:space="preserve">1474174</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J299">
-        <v>389</v>
+        <v>560</v>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t xml:space="preserve">311639215</t>
+          <t xml:space="preserve">311643479</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
@@ -22424,7 +22424,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-31</t>
+          <t xml:space="preserve">2032-11-18</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -22466,7 +22466,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindegårdsvej 3A</t>
+          <t xml:space="preserve">Vestermarken 3</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
@@ -22476,20 +22476,20 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699861</t>
+          <t xml:space="preserve">4450791</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J300">
-        <v>2443</v>
+        <v>1852</v>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643464</t>
+          <t xml:space="preserve">311643477</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
@@ -22541,7 +22541,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindegårdsvej 3B</t>
+          <t xml:space="preserve">Vestermarken 3</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
@@ -22551,20 +22551,20 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699861</t>
+          <t xml:space="preserve">4450791</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J301">
-        <v>1548</v>
+        <v>379</v>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643474</t>
+          <t xml:space="preserve">311643496</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
@@ -22616,7 +22616,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindegårdsvej 3D</t>
+          <t xml:space="preserve">Lindegårdsvej 3A</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
@@ -22631,15 +22631,15 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J302">
-        <v>2443</v>
+        <v>212</v>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643467</t>
+          <t xml:space="preserve">311649334</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
@@ -22649,7 +22649,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-18</t>
+          <t xml:space="preserve">2032-11-22</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -22691,7 +22691,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindegårdsvej 5</t>
+          <t xml:space="preserve">Lindegårdsvej 3C</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
@@ -22706,15 +22706,15 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J303">
-        <v>2011</v>
+        <v>2172</v>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643469</t>
+          <t xml:space="preserve">311644039</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
@@ -22724,7 +22724,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-18</t>
+          <t xml:space="preserve">2032-11-22</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -22766,30 +22766,30 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søbysøvej 7</t>
+          <t xml:space="preserve">Hovedgaden 32</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">6973</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t xml:space="preserve">1474174</t>
+          <t xml:space="preserve">4425011</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J304">
-        <v>560</v>
+        <v>1644</v>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643479</t>
+          <t xml:space="preserve">311646026</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
@@ -22799,7 +22799,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-18</t>
+          <t xml:space="preserve">2032-11-30</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -22841,30 +22841,30 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestermarken 3</t>
+          <t xml:space="preserve">Hovedgaden 32</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">6973</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450791</t>
+          <t xml:space="preserve">4425011</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J305">
-        <v>1852</v>
+        <v>586</v>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643477</t>
+          <t xml:space="preserve">311646032</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
@@ -22874,7 +22874,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-18</t>
+          <t xml:space="preserve">2032-11-30</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -22916,30 +22916,30 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestermarken 3</t>
+          <t xml:space="preserve">Skolegade 6</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7550</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t xml:space="preserve">4450791</t>
+          <t xml:space="preserve">4505959</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J306">
-        <v>379</v>
+        <v>4534</v>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t xml:space="preserve">311643496</t>
+          <t xml:space="preserve">311649340</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
@@ -22949,7 +22949,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-18</t>
+          <t xml:space="preserve">2032-12-15</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -22991,7 +22991,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindegårdsvej 3A</t>
+          <t xml:space="preserve">Skolesvinget 3</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
@@ -23001,20 +23001,20 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699861</t>
+          <t xml:space="preserve">4457315</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J307">
-        <v>212</v>
+        <v>1008</v>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t xml:space="preserve">311649334</t>
+          <t xml:space="preserve">311652347</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
@@ -23024,7 +23024,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-22</t>
+          <t xml:space="preserve">2033-01-04</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -23066,30 +23066,30 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lindegårdsvej 3C</t>
+          <t xml:space="preserve">Nørrevænget 4</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7480</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699861</t>
+          <t xml:space="preserve">4463109</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J308">
-        <v>2172</v>
+        <v>1169</v>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t xml:space="preserve">311644039</t>
+          <t xml:space="preserve">311653660</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
@@ -23099,7 +23099,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-22</t>
+          <t xml:space="preserve">2033-01-12</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -23141,17 +23141,17 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 32</t>
+          <t xml:space="preserve">Kirkegade 7</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t xml:space="preserve">6973</t>
+          <t xml:space="preserve">7480</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">4425011</t>
+          <t xml:space="preserve">4462864</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -23160,11 +23160,11 @@
         </is>
       </c>
       <c r="J309">
-        <v>1644</v>
+        <v>724</v>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646026</t>
+          <t xml:space="preserve">311654163</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
@@ -23174,7 +23174,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-30</t>
+          <t xml:space="preserve">2033-01-16</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -23216,30 +23216,30 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedgaden 32</t>
+          <t xml:space="preserve">Sydgaden 6</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t xml:space="preserve">6973</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">4425011</t>
+          <t xml:space="preserve">329553, 329554</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J310">
-        <v>586</v>
+        <v>3790</v>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t xml:space="preserve">311646032</t>
+          <t xml:space="preserve">311654167</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
@@ -23249,7 +23249,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-11-30</t>
+          <t xml:space="preserve">2033-01-16</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -23291,30 +23291,30 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 6</t>
+          <t xml:space="preserve">Østergade 2</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t xml:space="preserve">7550</t>
+          <t xml:space="preserve">7490</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t xml:space="preserve">4505959</t>
+          <t xml:space="preserve">334947, 334948</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J311">
-        <v>4534</v>
+        <v>4340</v>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t xml:space="preserve">311649340</t>
+          <t xml:space="preserve">311656515</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-15</t>
+          <t xml:space="preserve">2033-01-27</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -23366,7 +23366,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolesvinget 3</t>
+          <t xml:space="preserve">Nørregade 7A</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
@@ -23376,7 +23376,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t xml:space="preserve">4457315</t>
+          <t xml:space="preserve">7168779</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -23385,11 +23385,11 @@
         </is>
       </c>
       <c r="J312">
-        <v>1008</v>
+        <v>1614</v>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652347</t>
+          <t xml:space="preserve">311661414</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
@@ -23399,7 +23399,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-04</t>
+          <t xml:space="preserve">2033-02-21</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -23441,30 +23441,30 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrevænget 4</t>
+          <t xml:space="preserve">Nørregade 7A</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t xml:space="preserve">7480</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t xml:space="preserve">4463109</t>
+          <t xml:space="preserve">7168779</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J313">
-        <v>1169</v>
+        <v>1980</v>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t xml:space="preserve">311653660</t>
+          <t xml:space="preserve">311664324</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
@@ -23474,7 +23474,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-12</t>
+          <t xml:space="preserve">2033-03-06</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -23516,30 +23516,30 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kirkegade 7</t>
+          <t xml:space="preserve">Nørregade 7B</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t xml:space="preserve">7480</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t xml:space="preserve">4462864</t>
+          <t xml:space="preserve">7168779</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J314">
-        <v>724</v>
+        <v>420</v>
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654163</t>
+          <t xml:space="preserve">311664326</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
@@ -23549,7 +23549,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-16</t>
+          <t xml:space="preserve">2033-03-06</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -23591,7 +23591,7 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sydgaden 6</t>
+          <t xml:space="preserve">Nørregade 7C</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
@@ -23601,20 +23601,20 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t xml:space="preserve">329553, 329554</t>
+          <t xml:space="preserve">7168779</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J315">
-        <v>3790</v>
+        <v>1728</v>
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654167</t>
+          <t xml:space="preserve">311664329</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
@@ -23624,7 +23624,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-16</t>
+          <t xml:space="preserve">2033-03-06</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -23666,30 +23666,30 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 2</t>
+          <t xml:space="preserve">Nørregade 7D</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t xml:space="preserve">7490</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t xml:space="preserve">334947, 334948</t>
+          <t xml:space="preserve">7168779</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J316">
-        <v>4340</v>
+        <v>1106</v>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t xml:space="preserve">311656515</t>
+          <t xml:space="preserve">311664321</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
@@ -23699,7 +23699,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-27</t>
+          <t xml:space="preserve">2033-03-06</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -23741,7 +23741,7 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 7A</t>
+          <t xml:space="preserve">Hammerum Hovedgade 14</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
@@ -23751,7 +23751,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">7168779</t>
+          <t xml:space="preserve">8518026</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -23760,11 +23760,11 @@
         </is>
       </c>
       <c r="J317">
-        <v>1614</v>
+        <v>7138</v>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661414</t>
+          <t xml:space="preserve">311665603</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
@@ -23774,7 +23774,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-21</t>
+          <t xml:space="preserve">2033-03-10</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -23801,12 +23801,12 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herning Kommune</t>
+          <t xml:space="preserve">BOLIGSELSKABET FRUEHØJGAARD</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -23816,7 +23816,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 7A</t>
+          <t xml:space="preserve">Kousgaards Plads 4</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
@@ -23826,30 +23826,30 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">7168779</t>
+          <t xml:space="preserve">418274, 418275</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J318">
-        <v>1980</v>
+        <v>6809</v>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t xml:space="preserve">311664324</t>
+          <t xml:space="preserve">311665757</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-06</t>
+          <t xml:space="preserve">2033-03-11</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -23876,12 +23876,12 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herning Kommune</t>
+          <t xml:space="preserve">FællesBo</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
@@ -23891,40 +23891,40 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 7B</t>
+          <t xml:space="preserve">Skolegade 5</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7490</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">7168779</t>
+          <t xml:space="preserve">334945, 334946</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J319">
-        <v>420</v>
+        <v>2267</v>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t xml:space="preserve">311664326</t>
+          <t xml:space="preserve">311678734</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-06</t>
+          <t xml:space="preserve">2033-05-04</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -23966,7 +23966,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 7C</t>
+          <t xml:space="preserve">Mellemtoften 14</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
@@ -23976,20 +23976,20 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">7168779</t>
+          <t xml:space="preserve">4453352</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J320">
-        <v>1728</v>
+        <v>689</v>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t xml:space="preserve">311664329</t>
+          <t xml:space="preserve">311698577</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-06</t>
+          <t xml:space="preserve">2033-08-08</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -24041,7 +24041,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 7D</t>
+          <t xml:space="preserve">Bethaniagade 30</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -24051,20 +24051,20 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">7168779</t>
+          <t xml:space="preserve">5697779</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J321">
-        <v>1106</v>
+        <v>1189</v>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t xml:space="preserve">311664321</t>
+          <t xml:space="preserve">311698822</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
@@ -24074,7 +24074,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-06</t>
+          <t xml:space="preserve">2033-08-09</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -24116,17 +24116,17 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hammerum Hovedgade 14</t>
+          <t xml:space="preserve">Bjørnkærvej 1A</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7480</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">8518026</t>
+          <t xml:space="preserve">9835817</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -24135,11 +24135,11 @@
         </is>
       </c>
       <c r="J322">
-        <v>7138</v>
+        <v>264</v>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665603</t>
+          <t xml:space="preserve">311702712</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
@@ -24149,7 +24149,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-10</t>
+          <t xml:space="preserve">2033-08-25</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -24176,12 +24176,12 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOLIGSELSKABET FRUEHØJGAARD</t>
+          <t xml:space="preserve">Herning Kommune</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -24191,40 +24191,40 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kousgaards Plads 4</t>
+          <t xml:space="preserve">Bjørnkærvej 1B</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7480</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t xml:space="preserve">418274, 418275</t>
+          <t xml:space="preserve">9835817</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J323">
-        <v>6809</v>
+        <v>1197</v>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665757</t>
+          <t xml:space="preserve">311702713</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">EnergiTjenesten</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-11</t>
+          <t xml:space="preserve">2033-08-25</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -24251,12 +24251,12 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t xml:space="preserve">FællesBo</t>
+          <t xml:space="preserve">Herning Kommune</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -24266,40 +24266,40 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 5</t>
+          <t xml:space="preserve">Bjørnkærvej 1C</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t xml:space="preserve">7490</t>
+          <t xml:space="preserve">7480</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t xml:space="preserve">334945, 334946</t>
+          <t xml:space="preserve">9835817</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J324">
-        <v>2267</v>
+        <v>1225</v>
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t xml:space="preserve">311678734</t>
+          <t xml:space="preserve">311702714</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">EnergiTjenesten</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-04</t>
+          <t xml:space="preserve">2033-08-25</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -24341,30 +24341,30 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mellemtoften 14</t>
+          <t xml:space="preserve">Bjørnkærvej 1D</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7480</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">4453352</t>
+          <t xml:space="preserve">9835817</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J325">
-        <v>689</v>
+        <v>825</v>
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t xml:space="preserve">311698577</t>
+          <t xml:space="preserve">311702715</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-08</t>
+          <t xml:space="preserve">2033-08-25</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herning Kommune</t>
+          <t xml:space="preserve">FællesBo</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -24416,17 +24416,17 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bethaniagade 30</t>
+          <t xml:space="preserve">Nørregade 11</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7280</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">5697779</t>
+          <t xml:space="preserve">335411, 335412</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -24435,21 +24435,21 @@
         </is>
       </c>
       <c r="J326">
-        <v>1189</v>
+        <v>2485</v>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t xml:space="preserve">311698822</t>
+          <t xml:space="preserve">311703384</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-09</t>
+          <t xml:space="preserve">2033-08-29</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -24491,17 +24491,17 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjørnkærvej 1A</t>
+          <t xml:space="preserve">Sandagervej 39</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t xml:space="preserve">7480</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">9835817</t>
+          <t xml:space="preserve">5700223</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -24510,11 +24510,11 @@
         </is>
       </c>
       <c r="J327">
-        <v>264</v>
+        <v>609</v>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t xml:space="preserve">311702712</t>
+          <t xml:space="preserve">311704121</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
@@ -24524,7 +24524,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-25</t>
+          <t xml:space="preserve">2033-08-31</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -24566,30 +24566,30 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjørnkærvej 1B</t>
+          <t xml:space="preserve">Kollundvej 41</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t xml:space="preserve">7480</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t xml:space="preserve">9835817</t>
+          <t xml:space="preserve">4453567</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J328">
-        <v>1197</v>
+        <v>589</v>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t xml:space="preserve">311702713</t>
+          <t xml:space="preserve">311704317</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
@@ -24599,7 +24599,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-25</t>
+          <t xml:space="preserve">2033-09-01</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -24626,12 +24626,12 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herning Kommune</t>
+          <t xml:space="preserve">Lejerbo,Herning</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
@@ -24641,40 +24641,40 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjørnkærvej 1C</t>
+          <t xml:space="preserve">Sabroesvej 9A</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t xml:space="preserve">7480</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t xml:space="preserve">9835817</t>
+          <t xml:space="preserve">407269, 407270</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J329">
-        <v>1225</v>
+        <v>1745</v>
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t xml:space="preserve">311702714</t>
+          <t xml:space="preserve">311710650</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-25</t>
+          <t xml:space="preserve">2033-09-27</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -24716,30 +24716,30 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjørnkærvej 1D</t>
+          <t xml:space="preserve">Bethaniagade 6</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t xml:space="preserve">7480</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t xml:space="preserve">9835817</t>
+          <t xml:space="preserve">7952590</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J330">
-        <v>825</v>
+        <v>308</v>
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t xml:space="preserve">311702715</t>
+          <t xml:space="preserve">311712050</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
@@ -24749,7 +24749,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-25</t>
+          <t xml:space="preserve">2033-10-03</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -24776,12 +24776,12 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t xml:space="preserve">FællesBo</t>
+          <t xml:space="preserve">Herning Kommune</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -24791,17 +24791,17 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørregade 11</t>
+          <t xml:space="preserve">Bødkervej 1C</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t xml:space="preserve">7280</t>
+          <t xml:space="preserve">7451</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t xml:space="preserve">335411, 335412</t>
+          <t xml:space="preserve">100091782</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -24810,21 +24810,21 @@
         </is>
       </c>
       <c r="J331">
-        <v>2485</v>
+        <v>349</v>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t xml:space="preserve">311703384</t>
+          <t xml:space="preserve">311712048</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">EnergiTjenesten</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-29</t>
+          <t xml:space="preserve">2033-10-03</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -24866,7 +24866,7 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandagervej 39</t>
+          <t xml:space="preserve">Tolstedvej 22</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
@@ -24876,20 +24876,20 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700223</t>
+          <t xml:space="preserve">7740155</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J332">
-        <v>609</v>
+        <v>282</v>
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t xml:space="preserve">311704121</t>
+          <t xml:space="preserve">311712047</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
@@ -24899,7 +24899,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-31</t>
+          <t xml:space="preserve">2033-10-03</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -24941,7 +24941,7 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kollundvej 41</t>
+          <t xml:space="preserve">Gammel Løvbakkevej 2</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
@@ -24951,7 +24951,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t xml:space="preserve">4453567</t>
+          <t xml:space="preserve">329760</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -24960,11 +24960,11 @@
         </is>
       </c>
       <c r="J333">
-        <v>589</v>
+        <v>703</v>
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t xml:space="preserve">311704317</t>
+          <t xml:space="preserve">311729072</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
@@ -24974,7 +24974,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-01</t>
+          <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -25001,12 +25001,12 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lejerbo,Herning</t>
+          <t xml:space="preserve">Herning Kommune</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -25016,7 +25016,7 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sabroesvej 9A</t>
+          <t xml:space="preserve">Gammel Løvbakkevej 2</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
@@ -25026,30 +25026,30 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t xml:space="preserve">407269, 407270</t>
+          <t xml:space="preserve">329760</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J334">
-        <v>1745</v>
+        <v>343</v>
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t xml:space="preserve">311710650</t>
+          <t xml:space="preserve">311729073</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">EnergiTjenesten</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-09-27</t>
+          <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -25091,7 +25091,7 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bethaniagade 6</t>
+          <t xml:space="preserve">Trælundvej 1A</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
@@ -25101,20 +25101,20 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t xml:space="preserve">7952590</t>
+          <t xml:space="preserve">329760</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J335">
-        <v>308</v>
+        <v>919</v>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t xml:space="preserve">311712050</t>
+          <t xml:space="preserve">311729074</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
@@ -25124,7 +25124,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-03</t>
+          <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -25166,30 +25166,30 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bødkervej 1C</t>
+          <t xml:space="preserve">Trælundvej 1A</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t xml:space="preserve">7451</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t xml:space="preserve">100091782</t>
+          <t xml:space="preserve">329760</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J336">
-        <v>349</v>
+        <v>717</v>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t xml:space="preserve">311712048</t>
+          <t xml:space="preserve">311729075</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
@@ -25199,7 +25199,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-03</t>
+          <t xml:space="preserve">2033-12-14</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -25241,7 +25241,7 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tolstedvej 22</t>
+          <t xml:space="preserve">Studsgårdvej 25A</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
@@ -25251,30 +25251,30 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">7740155</t>
+          <t xml:space="preserve">100595167</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J337">
-        <v>282</v>
+        <v>410</v>
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t xml:space="preserve">311712047</t>
+          <t xml:space="preserve">311730337</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten</t>
+          <t xml:space="preserve">EnergiOptimo ApS</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-10-03</t>
+          <t xml:space="preserve">2033-12-20</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -25316,7 +25316,7 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Løvbakkevej 2</t>
+          <t xml:space="preserve">Gadegårdsvej 121</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
@@ -25326,7 +25326,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t xml:space="preserve">329760</t>
+          <t xml:space="preserve">9755163</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -25335,11 +25335,11 @@
         </is>
       </c>
       <c r="J338">
-        <v>703</v>
+        <v>6442</v>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729072</t>
+          <t xml:space="preserve">311731827</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
@@ -25349,7 +25349,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-14</t>
+          <t xml:space="preserve">2034-01-04</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -25391,7 +25391,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gammel Løvbakkevej 2</t>
+          <t xml:space="preserve">Markedspladsen 2</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
@@ -25401,20 +25401,20 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t xml:space="preserve">329760</t>
+          <t xml:space="preserve">332592</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J339">
-        <v>343</v>
+        <v>6642</v>
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729073</t>
+          <t xml:space="preserve">311733061</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-14</t>
+          <t xml:space="preserve">2034-01-12</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -25466,7 +25466,7 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trælundvej 1A</t>
+          <t xml:space="preserve">Vestergade 92</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
@@ -25476,20 +25476,20 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t xml:space="preserve">329760</t>
+          <t xml:space="preserve">5699376</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J340">
-        <v>919</v>
+        <v>9550</v>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729074</t>
+          <t xml:space="preserve">311737634</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
@@ -25499,7 +25499,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-14</t>
+          <t xml:space="preserve">2034-02-07</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -25541,7 +25541,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trælundvej 1A</t>
+          <t xml:space="preserve">Bjødstrupvej 60</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
@@ -25551,20 +25551,20 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">329760</t>
+          <t xml:space="preserve">10201137</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J341">
-        <v>717</v>
+        <v>223</v>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t xml:space="preserve">311729075</t>
+          <t xml:space="preserve">311780365</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
@@ -25574,7 +25574,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-14</t>
+          <t xml:space="preserve">2034-08-26</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -25616,7 +25616,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t xml:space="preserve">Studsgårdvej 25A</t>
+          <t xml:space="preserve">Gl. Ringkøbingvej 48</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
@@ -25626,30 +25626,30 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">100595167</t>
+          <t xml:space="preserve">5700816</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J342">
-        <v>410</v>
+        <v>109</v>
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t xml:space="preserve">311730337</t>
+          <t xml:space="preserve">311780362</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiOptimo ApS</t>
+          <t xml:space="preserve">EnergiTjenesten</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-12-20</t>
+          <t xml:space="preserve">2034-08-26</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -25691,17 +25691,17 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gadegårdsvej 121</t>
+          <t xml:space="preserve">Nøddevej 15</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7451</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t xml:space="preserve">9755163</t>
+          <t xml:space="preserve">4460820</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -25710,11 +25710,11 @@
         </is>
       </c>
       <c r="J343">
-        <v>6442</v>
+        <v>146</v>
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t xml:space="preserve">311731827</t>
+          <t xml:space="preserve">311780364</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
@@ -25724,7 +25724,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-04</t>
+          <t xml:space="preserve">2034-08-26</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -25766,7 +25766,7 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t xml:space="preserve">Markedspladsen 2</t>
+          <t xml:space="preserve">Skovvænget 2N</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
@@ -25776,20 +25776,20 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">332592</t>
+          <t xml:space="preserve">9827058</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J344">
-        <v>6642</v>
+        <v>496</v>
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t xml:space="preserve">311733061</t>
+          <t xml:space="preserve">311780363</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
@@ -25799,7 +25799,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-01-12</t>
+          <t xml:space="preserve">2034-08-26</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -25841,17 +25841,17 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 92</t>
+          <t xml:space="preserve">Velhustedvej 8</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">6933</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699376</t>
+          <t xml:space="preserve">4432076</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -25860,11 +25860,11 @@
         </is>
       </c>
       <c r="J345">
-        <v>9550</v>
+        <v>178</v>
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t xml:space="preserve">311737634</t>
+          <t xml:space="preserve">311780361</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
@@ -25874,7 +25874,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-02-07</t>
+          <t xml:space="preserve">2034-08-26</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -25916,30 +25916,30 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjødstrupvej 60</t>
+          <t xml:space="preserve">Østertoft 49A</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7490</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">10201137</t>
+          <t xml:space="preserve">4433851</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J346">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t xml:space="preserve">311780365</t>
+          <t xml:space="preserve">311780366</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
@@ -25991,7 +25991,7 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Ringkøbingvej 48</t>
+          <t xml:space="preserve">Fuglsang Toft 4</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
@@ -26001,7 +26001,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700816</t>
+          <t xml:space="preserve">100052096</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -26010,11 +26010,11 @@
         </is>
       </c>
       <c r="J347">
-        <v>109</v>
+        <v>11240</v>
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t xml:space="preserve">311780362</t>
+          <t xml:space="preserve">311784417</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
@@ -26024,7 +26024,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-26</t>
+          <t xml:space="preserve">2034-09-12</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -26051,12 +26051,12 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herning Kommune</t>
+          <t xml:space="preserve">Fastrupdalen ApS</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -26066,17 +26066,17 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nøddevej 15</t>
+          <t xml:space="preserve">Fastrupdalen 40</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t xml:space="preserve">7451</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t xml:space="preserve">4460820</t>
+          <t xml:space="preserve">100684596</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -26085,21 +26085,21 @@
         </is>
       </c>
       <c r="J348">
-        <v>146</v>
+        <v>4210</v>
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t xml:space="preserve">311780364</t>
+          <t xml:space="preserve">311790345</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-26</t>
+          <t xml:space="preserve">2034-10-09</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -26141,7 +26141,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvænget 2N</t>
+          <t xml:space="preserve">Hammerum Hovedgade 8</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
@@ -26151,30 +26151,30 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t xml:space="preserve">9827058</t>
+          <t xml:space="preserve">9949194</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J349">
-        <v>496</v>
+        <v>314</v>
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t xml:space="preserve">311780363</t>
+          <t xml:space="preserve">311807464</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-26</t>
+          <t xml:space="preserve">2035-01-23</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -26216,17 +26216,17 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t xml:space="preserve">Velhustedvej 8</t>
+          <t xml:space="preserve">Teglvænget 10</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t xml:space="preserve">6933</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t xml:space="preserve">4432076</t>
+          <t xml:space="preserve">5703577</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -26235,21 +26235,21 @@
         </is>
       </c>
       <c r="J350">
-        <v>178</v>
+        <v>132</v>
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t xml:space="preserve">311780361</t>
+          <t xml:space="preserve">311808932</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten</t>
+          <t xml:space="preserve">OBH</t>
         </is>
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-26</t>
+          <t xml:space="preserve">2035-01-30</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -26291,30 +26291,30 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østertoft 49A</t>
+          <t xml:space="preserve">Gl. Landevej 61</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t xml:space="preserve">7490</t>
+          <t xml:space="preserve">7400</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t xml:space="preserve">4433851</t>
+          <t xml:space="preserve">9386416</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="J351">
-        <v>248</v>
+        <v>11187</v>
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t xml:space="preserve">311780366</t>
+          <t xml:space="preserve">311827530</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
@@ -26324,7 +26324,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-26</t>
+          <t xml:space="preserve">2035-04-28</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -26366,7 +26366,7 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fuglsang Toft 4</t>
+          <t xml:space="preserve">Gl. Landevej 61</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
@@ -26376,20 +26376,20 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t xml:space="preserve">100052096</t>
+          <t xml:space="preserve">9386416</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="J352">
-        <v>11240</v>
+        <v>119</v>
       </c>
       <c r="K352" t="inlineStr">
         <is>
-          <t xml:space="preserve">311784417</t>
+          <t xml:space="preserve">311827530</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
@@ -26399,7 +26399,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-09-12</t>
+          <t xml:space="preserve">2035-04-28</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -26426,12 +26426,12 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fastrupdalen ApS</t>
+          <t xml:space="preserve">Herning Kommune</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -26441,7 +26441,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fastrupdalen 40</t>
+          <t xml:space="preserve">Gl. Landevej 61</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
@@ -26451,30 +26451,30 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t xml:space="preserve">100684596</t>
+          <t xml:space="preserve">9386416</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">55</t>
         </is>
       </c>
       <c r="J353">
-        <v>4210</v>
+        <v>1164</v>
       </c>
       <c r="K353" t="inlineStr">
         <is>
-          <t xml:space="preserve">311790345</t>
+          <t xml:space="preserve">311827530</t>
         </is>
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">EnergiTjenesten</t>
         </is>
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-10-09</t>
+          <t xml:space="preserve">2035-04-28</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -26516,7 +26516,7 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hammerum Hovedgade 8</t>
+          <t xml:space="preserve">Gl. Landevej 71</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
@@ -26526,30 +26526,30 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t xml:space="preserve">9949194</t>
+          <t xml:space="preserve">9386416</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">37</t>
         </is>
       </c>
       <c r="J354">
-        <v>314</v>
+        <v>7390</v>
       </c>
       <c r="K354" t="inlineStr">
         <is>
-          <t xml:space="preserve">311807464</t>
+          <t xml:space="preserve">311827530</t>
         </is>
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+          <t xml:space="preserve">EnergiTjenesten</t>
         </is>
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-01-23</t>
+          <t xml:space="preserve">2035-04-28</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -26591,7 +26591,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t xml:space="preserve">Teglvænget 10</t>
+          <t xml:space="preserve">Møllegade 16</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
@@ -26601,30 +26601,30 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t xml:space="preserve">5703577</t>
+          <t xml:space="preserve">9386416</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">50</t>
         </is>
       </c>
       <c r="J355">
-        <v>132</v>
+        <v>4622</v>
       </c>
       <c r="K355" t="inlineStr">
         <is>
-          <t xml:space="preserve">311808932</t>
+          <t xml:space="preserve">311827530</t>
         </is>
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH</t>
+          <t xml:space="preserve">EnergiTjenesten</t>
         </is>
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-01-30</t>
+          <t xml:space="preserve">2035-04-28</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -26666,7 +26666,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Landevej 61</t>
+          <t xml:space="preserve">Overgade 22</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
@@ -26681,11 +26681,11 @@
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t xml:space="preserve">33</t>
+          <t xml:space="preserve">53</t>
         </is>
       </c>
       <c r="J356">
-        <v>11187</v>
+        <v>494</v>
       </c>
       <c r="K356" t="inlineStr">
         <is>
@@ -26741,7 +26741,7 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Landevej 61</t>
+          <t xml:space="preserve">Overgade 4</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
@@ -26756,11 +26756,11 @@
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t xml:space="preserve">34</t>
+          <t xml:space="preserve">29</t>
         </is>
       </c>
       <c r="J357">
-        <v>119</v>
+        <v>1327</v>
       </c>
       <c r="K357" t="inlineStr">
         <is>
@@ -26816,7 +26816,7 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Landevej 61</t>
+          <t xml:space="preserve">Østergade 8</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
@@ -26826,20 +26826,20 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t xml:space="preserve">9386416</t>
+          <t xml:space="preserve">5697359</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t xml:space="preserve">55</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J358">
-        <v>1164</v>
+        <v>5468</v>
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t xml:space="preserve">311827530</t>
+          <t xml:space="preserve">311837610</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
@@ -26849,7 +26849,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-28</t>
+          <t xml:space="preserve">2035-06-12</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -26891,7 +26891,7 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Landevej 71</t>
+          <t xml:space="preserve">Tavlund Krat 23</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
@@ -26901,30 +26901,30 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t xml:space="preserve">9386416</t>
+          <t xml:space="preserve">100758159</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t xml:space="preserve">37</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J359">
-        <v>7390</v>
+        <v>130</v>
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t xml:space="preserve">311827530</t>
+          <t xml:space="preserve">311838002</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten</t>
+          <t xml:space="preserve">Dansk Energisyn ApS</t>
         </is>
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-28</t>
+          <t xml:space="preserve">2035-06-13</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -26966,7 +26966,7 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t xml:space="preserve">Møllegade 16</t>
+          <t xml:space="preserve">Snejbjerg Hovedgade 75</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
@@ -26976,20 +26976,20 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t xml:space="preserve">9386416</t>
+          <t xml:space="preserve">329181</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t xml:space="preserve">50</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J360">
-        <v>4622</v>
+        <v>11385</v>
       </c>
       <c r="K360" t="inlineStr">
         <is>
-          <t xml:space="preserve">311827530</t>
+          <t xml:space="preserve">311899308</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
@@ -26999,7 +26999,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-28</t>
+          <t xml:space="preserve">2035-08-26</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -27041,7 +27041,7 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overgade 22</t>
+          <t xml:space="preserve">Kousgaards Plads 1</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
@@ -27051,20 +27051,20 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t xml:space="preserve">9386416</t>
+          <t xml:space="preserve">329484, 329485, 329486, 329487, 329488, 329489, 329490, 329491, 329492, 329510, 329493, 329494, 329495, 329496, 329497, 329498, 329499, 329500, 329502, 329503, 329504, 329505, 329506, 329507, 329508, 329509</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t xml:space="preserve">53</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J361">
-        <v>494</v>
+        <v>18167</v>
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t xml:space="preserve">311827530</t>
+          <t xml:space="preserve">311858702</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
@@ -27074,7 +27074,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-28</t>
+          <t xml:space="preserve">2035-09-29</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -27116,7 +27116,7 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overgade 4</t>
+          <t xml:space="preserve">Skovvænget 2C</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
@@ -27126,20 +27126,20 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t xml:space="preserve">9386416</t>
+          <t xml:space="preserve">9827058</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t xml:space="preserve">29</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J362">
-        <v>1327</v>
+        <v>238</v>
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t xml:space="preserve">311827530</t>
+          <t xml:space="preserve">311870967</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
@@ -27149,7 +27149,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-04-28</t>
+          <t xml:space="preserve">2035-12-01</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -27191,7 +27191,7 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østergade 8</t>
+          <t xml:space="preserve">Skovvænget 2F</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
@@ -27201,20 +27201,20 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t xml:space="preserve">5697359</t>
+          <t xml:space="preserve">9827058</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J363">
-        <v>5468</v>
+        <v>238</v>
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t xml:space="preserve">311837610</t>
+          <t xml:space="preserve">311870968</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
@@ -27224,7 +27224,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-12</t>
+          <t xml:space="preserve">2035-12-01</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -27266,7 +27266,7 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tavlund Krat 23</t>
+          <t xml:space="preserve">Skovvænget 2K</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
@@ -27276,30 +27276,30 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t xml:space="preserve">100758159</t>
+          <t xml:space="preserve">9827058</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J364">
-        <v>130</v>
+        <v>238</v>
       </c>
       <c r="K364" t="inlineStr">
         <is>
-          <t xml:space="preserve">311838002</t>
+          <t xml:space="preserve">311870970</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Energisyn ApS</t>
+          <t xml:space="preserve">EnergiTjenesten</t>
         </is>
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-13</t>
+          <t xml:space="preserve">2035-12-01</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -27341,7 +27341,7 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t xml:space="preserve">Snejbjerg Hovedgade 75</t>
+          <t xml:space="preserve">Vestergade 82A</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
@@ -27351,20 +27351,20 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t xml:space="preserve">329181</t>
+          <t xml:space="preserve">5699393, 100261403</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J365">
-        <v>11385</v>
+        <v>242</v>
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t xml:space="preserve">311899308</t>
+          <t xml:space="preserve">311884101</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
@@ -27374,7 +27374,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-26</t>
+          <t xml:space="preserve">2036-02-25</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -27416,7 +27416,7 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kousgaards Plads 1</t>
+          <t xml:space="preserve">Gilmosevej 26</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
@@ -27426,7 +27426,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t xml:space="preserve">329484, 329485, 329486, 329487, 329488, 329489, 329490, 329491, 329492, 329510, 329493, 329494, 329495, 329496, 329497, 329498, 329499, 329500, 329502, 329503, 329504, 329505, 329506, 329507, 329508, 329509</t>
+          <t xml:space="preserve">9266760</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -27435,11 +27435,11 @@
         </is>
       </c>
       <c r="J366">
-        <v>18167</v>
+        <v>219</v>
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858702</t>
+          <t xml:space="preserve">311902868</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
@@ -27449,7 +27449,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-29</t>
+          <t xml:space="preserve">2036-05-21</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -27491,7 +27491,7 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvænget 2C</t>
+          <t xml:space="preserve">Vesterlindvej 21</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
@@ -27501,20 +27501,20 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t xml:space="preserve">9827058</t>
+          <t xml:space="preserve">4452247</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J367">
-        <v>238</v>
+        <v>264</v>
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t xml:space="preserve">311870967</t>
+          <t xml:space="preserve">311905571</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-01</t>
+          <t xml:space="preserve">2036-06-04</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -27551,12 +27551,12 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direkte ejer</t>
+          <t xml:space="preserve">Medejer</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t xml:space="preserve">Herning Kommune</t>
+          <t xml:space="preserve">EJENDOMSSELSKABET ÅGÅRDSVEJ 2 ApS</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -27566,40 +27566,40 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvænget 2F</t>
+          <t xml:space="preserve">Ågårdsvej 2A</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7480</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t xml:space="preserve">9827058</t>
+          <t xml:space="preserve">334130, 334131, 334132</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J368">
-        <v>238</v>
+        <v>2352</v>
       </c>
       <c r="K368" t="inlineStr">
         <is>
-          <t xml:space="preserve">311870968</t>
+          <t xml:space="preserve">311913941</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t xml:space="preserve">EnergiTjenesten</t>
+          <t xml:space="preserve">Lemvig Arkitektkontor Aps</t>
         </is>
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-01</t>
+          <t xml:space="preserve">2036-07-09</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -27641,30 +27641,30 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovvænget 2K</t>
+          <t xml:space="preserve">Gyvelvej 5</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7550</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t xml:space="preserve">9827058</t>
+          <t xml:space="preserve">4506406</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J369">
-        <v>238</v>
+        <v>498</v>
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t xml:space="preserve">311870970</t>
+          <t xml:space="preserve">311928799</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
@@ -27674,7 +27674,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-01</t>
+          <t xml:space="preserve">2036-09-29</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -27716,30 +27716,30 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestergade 82A</t>
+          <t xml:space="preserve">Gyvelvej 5</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">7550</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t xml:space="preserve">5699393, 100261403</t>
+          <t xml:space="preserve">4506406</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J370">
-        <v>242</v>
+        <v>77</v>
       </c>
       <c r="K370" t="inlineStr">
         <is>
-          <t xml:space="preserve">311884101</t>
+          <t xml:space="preserve">311928798</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
@@ -27749,7 +27749,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-25</t>
+          <t xml:space="preserve">2036-09-29</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -27791,7 +27791,7 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gilmosevej 26</t>
+          <t xml:space="preserve">Haugevej 25</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
@@ -27801,7 +27801,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t xml:space="preserve">9266760</t>
+          <t xml:space="preserve">100063131</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -27810,11 +27810,11 @@
         </is>
       </c>
       <c r="J371">
-        <v>219</v>
+        <v>1683</v>
       </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t xml:space="preserve">311902868</t>
+          <t xml:space="preserve">311928800</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
@@ -27824,7 +27824,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-05-21</t>
+          <t xml:space="preserve">2036-09-29</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -27866,30 +27866,30 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vesterlindvej 21</t>
+          <t xml:space="preserve">Skolevejen 6</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t xml:space="preserve">7400</t>
+          <t xml:space="preserve">6933</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t xml:space="preserve">4452247</t>
+          <t xml:space="preserve">4455442</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J372">
-        <v>264</v>
+        <v>2812</v>
       </c>
       <c r="K372" t="inlineStr">
         <is>
-          <t xml:space="preserve">311905571</t>
+          <t xml:space="preserve">311928795</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
@@ -27899,7 +27899,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-06-04</t>
+          <t xml:space="preserve">2036-09-29</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -27926,12 +27926,12 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medejer</t>
+          <t xml:space="preserve">Direkte ejer</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t xml:space="preserve">EJENDOMSSELSKABET ÅGÅRDSVEJ 2 ApS</t>
+          <t xml:space="preserve">Herning Kommune</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
@@ -27941,40 +27941,40 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ågårdsvej 2A</t>
+          <t xml:space="preserve">Skolevejen 6</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t xml:space="preserve">7480</t>
+          <t xml:space="preserve">6933</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t xml:space="preserve">334130, 334131, 334132</t>
+          <t xml:space="preserve">4455442</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J373">
-        <v>2352</v>
+        <v>386</v>
       </c>
       <c r="K373" t="inlineStr">
         <is>
-          <t xml:space="preserve">311913941</t>
+          <t xml:space="preserve">311928797</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lemvig Arkitektkontor Aps</t>
+          <t xml:space="preserve">EnergiTjenesten</t>
         </is>
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-09</t>
+          <t xml:space="preserve">2036-09-29</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
